--- a/data/output/corpus_run_v7_web_500/queries.xlsx
+++ b/data/output/corpus_run_v7_web_500/queries.xlsx
@@ -11610,19 +11610,19 @@
         <v>medium</v>
       </c>
       <c r="H295">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I295">
-        <v>91183</v>
+        <v>0</v>
       </c>
       <c r="J295" t="str">
-        <v/>
+        <v>Need a community changelog tracker web app where every time we ship something new, users can see the update and actually react to it or leave a comment thread right underneath, so there's a back-and-forth conversation tied to each release, and the main list on the left shows all the entries in order while clicking one opens the discussion on the right side of the browser.</v>
       </c>
       <c r="K295" t="str">
-        <v/>
+        <v>需要一个社区更新日志追踪网站，每次发布新功能，用户都能看到更新内容，还可以给下面的讨论贴进行反应或者留言讨论，形成围绕每个发布版本的对话，左边的列表按顺序显示所有条目，点击某一条就在右侧打开对应的讨论内容。</v>
       </c>
       <c r="L295" t="str">
-        <v>[q_web_042_007] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="296">
@@ -11762,19 +11762,19 @@
         <v>medium</v>
       </c>
       <c r="H299">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I299">
-        <v>62443</v>
+        <v>0</v>
       </c>
       <c r="J299" t="str">
-        <v/>
+        <v>Create a web app that works as a documentation hub for our SaaS developer tools, so anyone who wants to use our APIs can just open a browser and look up what they need in one place — I want a left sidebar listing all the different tools and endpoints, and when you click one it shows the full reference guide with example requests right next to it, so developers stop emailing us asking basic questions.</v>
       </c>
       <c r="K299" t="str">
-        <v/>
+        <v>创建一个 SaaS 开发者工具文档中心网站，这样需要使用 API 的用户就能在浏览器里一站式查看所有文档——左边侧栏列出不同的工具和端点，点击后右边就显示完整的 API 参考指南以及请求示例，这样开发者就不用邮件问我们基础问题了。</v>
       </c>
       <c r="L299" t="str">
-        <v>[q_web_043_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="300">
@@ -11838,19 +11838,19 @@
         <v>medium</v>
       </c>
       <c r="H301">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I301">
-        <v>67692</v>
+        <v>0</v>
       </c>
       <c r="J301" t="str">
-        <v/>
+        <v>Build a web app that helps you put together a step-by-step onboarding checklist for new SaaS customers, where you can add tasks, group them into stages like setup and first use, and customers can tick things off as they go so nobody gets lost trying to figure out what to do next after signing up.</v>
       </c>
       <c r="K301" t="str">
-        <v/>
+        <v>构建一个 SaaS 用户入门清单网站，可以添加任务、分组到不同阶段（比如初始化和首次使用），用户可以一项一项勾选完成，这样注册后就不会困惑接下来应该做什么。</v>
       </c>
       <c r="L301" t="str">
-        <v>[q_web_043_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="302">
@@ -11914,19 +11914,19 @@
         <v>medium</v>
       </c>
       <c r="H303">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I303">
-        <v>22369</v>
+        <v>0</v>
       </c>
       <c r="J303" t="str">
-        <v/>
+        <v>Build a website for a school that covers all the basics — a home section introducing who we are, a list of our programs and courses, information about teachers, and a news or announcements area — all organized so visitors can click through and find what they need easily when browsing on a desktop browser.</v>
       </c>
       <c r="K303" t="str">
-        <v/>
+        <v>为学校创建一个网站，包含所有基础内容——首页介绍学校背景、课程和项目列表、教师信息以及新闻或公告区域——所有内容井井有条，访客可以点击浏览，在桌面浏览器上轻松找到需要的信息。</v>
       </c>
       <c r="L303" t="str">
-        <v>[q_web_044_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="304">
@@ -11952,19 +11952,19 @@
         <v>medium</v>
       </c>
       <c r="H304">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I304">
-        <v>22405</v>
+        <v>0</v>
       </c>
       <c r="J304" t="str">
-        <v/>
+        <v>Create a campus life showcase website for our school where we can display photos and highlights from student activities, club events, and daily campus moments, with a browsable gallery organized by category so visitors on a desktop browser can get a real feel for what life on campus actually looks like.</v>
       </c>
       <c r="K304" t="str">
-        <v/>
+        <v>为学校建立一个校园生活展示网站，展示学生活动、社团活动和校园日常的照片和精彩内容，按类别组织可浏览的相册，让访客在桌面浏览器上能真实感受校园生活的样子。</v>
       </c>
       <c r="L304" t="str">
-        <v>[q_web_044_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="305">
@@ -11990,19 +11990,19 @@
         <v>medium</v>
       </c>
       <c r="H305">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I305">
-        <v>21058</v>
+        <v>0</v>
       </c>
       <c r="J305" t="str">
-        <v/>
+        <v>An app that shows off our school's teaching team on a website, where each teacher has their own card listing their name, subject, a short bio, and a photo, and visitors can browse all the teachers or filter by department, so parents and students always know who's who when they open it in a desktop browser.</v>
       </c>
       <c r="K305" t="str">
-        <v/>
+        <v>开发一个展示学校教师团队的网站，每个教师有独立的卡片，显示名字、教学科目、简介和照片，访客可以浏览所有教师或按部门筛选，家长和学生在桌面浏览器上打开时能清楚地了解每位教师。</v>
       </c>
       <c r="L305" t="str">
-        <v>[q_web_044_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="306">
@@ -12028,19 +12028,19 @@
         <v>medium</v>
       </c>
       <c r="H306">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I306">
-        <v>25804</v>
+        <v>0</v>
       </c>
       <c r="J306" t="str">
-        <v/>
+        <v>Make a university course catalog website where students can browse all the programs and individual classes offered, filter by department or level, and click into any course to see the description, credit hours, and requirements — basically a clean reference tool they can use on a desktop browser when planning out their studies.</v>
       </c>
       <c r="K306" t="str">
-        <v/>
+        <v>制作一个大学课程目录网站，学生可以浏览所有课程和项目、按院系或难度筛选、点击任何课程查看描述、学分和要求——基本上就是一个简洁的参考工具，他们在桌面浏览器上规划学业时可以随时查看。</v>
       </c>
       <c r="L306" t="str">
-        <v>[q_web_044_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="307">
@@ -12066,19 +12066,19 @@
         <v>medium</v>
       </c>
       <c r="H307">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="I307">
-        <v>40296</v>
+        <v>0</v>
       </c>
       <c r="J307" t="str">
-        <v/>
+        <v>An alumni success stories website where we collect and display profiles of graduates who've gone on to interesting careers, with their name, graduating year, current role, and a short story about how they got there, organized so visitors can browse by industry or year when looking at it on a desktop browser.</v>
       </c>
       <c r="K307" t="str">
-        <v/>
+        <v>建立一个校友成功故事网站，展示毕业后进入有趣职业领域的校友档案，包含名字、毕业年份、当前职位和他们如何走到今天的简短故事，访客在桌面浏览器上可以按行业或年份浏览。</v>
       </c>
       <c r="L307" t="str">
-        <v>[q_web_044_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="308">
@@ -12104,19 +12104,19 @@
         <v>medium</v>
       </c>
       <c r="H308">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I308">
-        <v>20766</v>
+        <v>0</v>
       </c>
       <c r="J308" t="str">
-        <v/>
+        <v>Need a website that displays all the official accreditations and awards our school has earned, so prospective students and parents can see at a glance what certifications we hold and what recognition we've received, with each item showing the name, issuing body, and the year it was granted, all laid out nicely for desktop browsers.</v>
       </c>
       <c r="K308" t="str">
-        <v/>
+        <v>需要一个展示学校所有官方认证和荣誉奖项的网站，这样潜在学生和家长可以一目了然地看到我们拥有哪些资质和获得了什么认可，每项显示名称、颁发机构和授予年份，在桌面浏览器上布局美观。</v>
       </c>
       <c r="L308" t="str">
-        <v>[q_web_044_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="309">
@@ -12142,19 +12142,19 @@
         <v>medium</v>
       </c>
       <c r="H309">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I309">
-        <v>22478</v>
+        <v>0</v>
       </c>
       <c r="J309" t="str">
-        <v/>
+        <v>Make a student project gallery website where graduating students can showcase their final capstone projects, with each project card showing the title, student name, a brief description, and a photo or screenshot, and visitors can filter by subject area or graduation year to find what interests them when browsing on a desktop browser.</v>
       </c>
       <c r="K309" t="str">
-        <v/>
+        <v>制作一个学生项目作品展示网站，毕业学生可以展示他们的毕设项目，每个项目卡片显示标题、学生名字、简要描述和照片或截图，访客可以按学科或毕业年份筛选，在桌面浏览器上浏览感兴趣的内容。</v>
       </c>
       <c r="L309" t="str">
-        <v>[q_web_044_007] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="310">
@@ -12180,19 +12180,19 @@
         <v>medium</v>
       </c>
       <c r="H310">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I310">
-        <v>25640</v>
+        <v>0</v>
       </c>
       <c r="J310" t="str">
-        <v/>
+        <v>Need a campus news website where the school can post announcements and stories organized by date, with a sidebar listing categories like events, achievements, and notices so readers can click through to find what they care about, and each article opens up with the full text and any related photos — all readable comfortably in a desktop browser.</v>
       </c>
       <c r="K310" t="str">
-        <v/>
+        <v>需要一个校园新闻网站，学校可以按日期发布公告和新闻，侧栏列出活动、成就和通知等分类，读者可以点击浏览关心的内容，每篇文章打开后显示完整文本和相关照片——在桌面浏览器上舒适阅读。</v>
       </c>
       <c r="L310" t="str">
-        <v>[q_web_045_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="311">
@@ -12218,19 +12218,19 @@
         <v>medium</v>
       </c>
       <c r="H311">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I311">
-        <v>25170</v>
+        <v>0</v>
       </c>
       <c r="J311" t="str">
-        <v/>
+        <v>Make a web app where faculty members can list all their published papers and academic work in one place, with each entry showing the title, co-authors, the journal or conference it appeared in, and the year, so anyone browsing on a desktop browser can get a clear picture of a researcher's publication history without hunting across different sites.</v>
       </c>
       <c r="K311" t="str">
-        <v/>
+        <v>开发一个网站让教师可以在一个地方列出所有已发表的论文和学术成果，每个条目显示标题、合作者、发表的期刊或会议以及年份，这样访客在桌面浏览器上可以清楚地了解研究人员的发表历史，无需在多个网站间寻找。</v>
       </c>
       <c r="L311" t="str">
-        <v>[q_web_045_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="312">
@@ -12256,19 +12256,19 @@
         <v>medium</v>
       </c>
       <c r="H312">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I312">
-        <v>21396</v>
+        <v>0</v>
       </c>
       <c r="J312" t="str">
-        <v/>
+        <v>A research outcomes website for our university where we collect and display all the projects and findings from our labs and departments, with each entry showing the project name, the team behind it, a short plain-language summary, and any publications linked to it, so anyone on a desktop browser can browse what our researchers have been working on.</v>
       </c>
       <c r="K312" t="str">
-        <v/>
+        <v>为我们的大学建立一个研究成果网站，展示实验室和部门的所有项目和研究发现，每个条目显示项目名称、团队成员、平实易懂的总结和相关出版物链接，访客在桌面浏览器上可以浏览研究人员的工作成果。</v>
       </c>
       <c r="L312" t="str">
-        <v>[q_web_045_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="313">
@@ -12294,19 +12294,19 @@
         <v>medium</v>
       </c>
       <c r="H313">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I313">
-        <v>22185</v>
+        <v>0</v>
       </c>
       <c r="J313" t="str">
-        <v/>
+        <v>An education news and information website where we keep a running list of articles about what's happening in schools and learning — things like policy updates, teaching trends, and study tips — organized by topic so readers can browse through categories and find what's relevant to them when they open it in a desktop browser.</v>
       </c>
       <c r="K313" t="str">
-        <v/>
+        <v>建立一个教育新闻和信息网站，持续更新学校和教育领域的相关文章——比如政策更新、教学趋势和学习建议——按主题组织，读者可以浏览不同类别，在桌面浏览器上找到相关内容。</v>
       </c>
       <c r="L313" t="str">
-        <v>[q_web_045_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="314">
@@ -12332,19 +12332,19 @@
         <v>medium</v>
       </c>
       <c r="H314">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I314">
-        <v>21490</v>
+        <v>0</v>
       </c>
       <c r="J314" t="str">
-        <v/>
+        <v>Build a website that works as a directory of our university's faculty, where each professor has a profile showing their name, department, research interests, a short biography, and a list of their recent publications, so students and collaborators can look someone up and understand their work quickly when browsing on a desktop browser.</v>
       </c>
       <c r="K314" t="str">
-        <v/>
+        <v>建立一个大学教师目录网站，每个教授有个人档案，显示名字、部门、研究方向、简历和最近发表的论文，学生和合作者在桌面浏览器上可以快速查找和了解他们的工作。</v>
       </c>
       <c r="L314" t="str">
-        <v>[q_web_045_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="315">
@@ -12370,19 +12370,19 @@
         <v>medium</v>
       </c>
       <c r="H315">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="I315">
-        <v>23275</v>
+        <v>0</v>
       </c>
       <c r="J315" t="str">
-        <v/>
+        <v>Make a web app that reads like an online magazine for alumni stories, where each article follows one graduate's career path from school to where they are now, with their name, graduating year, industry, and a first-person account of their journey, and the homepage shows a browsable list of featured stories people can read through in a desktop browser.</v>
       </c>
       <c r="K315" t="str">
-        <v/>
+        <v>开发一个在线杂志风格的校友故事网站，每篇文章讲述一位毕业生从学校到现在的职业发展历程，包含名字、毕业年份、所在行业和第一人称的人生故事，首页显示可浏览的精选故事列表，访客在桌面浏览器上阅读。</v>
       </c>
       <c r="L315" t="str">
-        <v>[q_web_045_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="316">
@@ -12408,19 +12408,19 @@
         <v>medium</v>
       </c>
       <c r="H316">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I316">
-        <v>21977</v>
+        <v>0</v>
       </c>
       <c r="J316" t="str">
-        <v/>
+        <v>Build a website where students and learners can find free course materials and lecture notes organized by subject, with each course listed by name, topic area, and instructor so people can quickly find what they need, and clicking a course shows all the available downloads or links — easy to navigate on a desktop browser without needing to register or pay.</v>
       </c>
       <c r="K316" t="str">
-        <v/>
+        <v>建立一个网站让学生和学习者可以找到免费的课程材料和讲义，按科目组织，每个课程按名称、主题和授课教师列出，这样人们可以快速找到需要的内容，点击课程显示所有可用的下载或链接——在桌面浏览器上易于导航，无需注册或付费。</v>
       </c>
       <c r="L316" t="str">
-        <v>[q_web_045_007] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="317">
@@ -12446,19 +12446,19 @@
         <v>medium</v>
       </c>
       <c r="H317">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I317">
-        <v>22454</v>
+        <v>0</v>
       </c>
       <c r="J317" t="str">
-        <v/>
+        <v>An admissions information website for our school, with all the key things a prospective student or parent would want to know — application steps, deadlines, required documents, tuition fees, and a short intro about what makes our programs worth joining — laid out clearly so someone browsing on a desktop browser can get through all of it without needing to call us.</v>
       </c>
       <c r="K317" t="str">
-        <v/>
+        <v>为学校建立招生信息网站，包含潜在学生或家长想了解的所有要点——申请步骤、截止日期、所需文件、学费以及项目值得加入的简短介绍——清晰地展示，这样在桌面浏览器上浏览的人不用打电话就能了解全部信息。</v>
       </c>
       <c r="L317" t="str">
-        <v>[q_web_046_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="318">
@@ -12484,19 +12484,19 @@
         <v>medium</v>
       </c>
       <c r="H318">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="I318">
-        <v>28959</v>
+        <v>0</v>
       </c>
       <c r="J318" t="str">
-        <v/>
+        <v>Build a course promotion website where we can present each of our classes with a clear title, a description of what students will learn, who the instructor is, how long it runs, and what it costs, so people browsing on a desktop browser can compare our offerings and decide which one they want to sign up for.</v>
       </c>
       <c r="K318" t="str">
-        <v/>
+        <v>建立一个课程推广网站，展示每个课程的清晰标题、学生将学到什么、授课教师是谁、课程周期和费用，访客在桌面浏览器上可以比较我们的课程并决定报名参加哪一个。</v>
       </c>
       <c r="L318" t="str">
-        <v>[q_web_046_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="319">
@@ -12522,19 +12522,19 @@
         <v>medium</v>
       </c>
       <c r="H319">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I319">
-        <v>22040</v>
+        <v>0</v>
       </c>
       <c r="J319" t="str">
-        <v/>
+        <v>Need a web app that helps promote our open online classes, where we list each upcoming course with the topic, instructor name, schedule, and how to join for free, and someone on a desktop browser can browse through all available classes and sign up directly from the page without having to dig through emails or PDFs to find the information.</v>
       </c>
       <c r="K319" t="str">
-        <v/>
+        <v>需要一个网站推广开放在线课程，列出每个即将开始的课程及其主题、讲师名字、时间安排和免费加入方式，这样访客在桌面浏览器上可以浏览所有可用课程并直接报名，无需通过邮件或 PDF 查找信息。</v>
       </c>
       <c r="L319" t="str">
-        <v>[q_web_046_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="320">
@@ -12560,19 +12560,19 @@
         <v>medium</v>
       </c>
       <c r="H320">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="I320">
-        <v>23150</v>
+        <v>0</v>
       </c>
       <c r="J320" t="str">
-        <v/>
+        <v>Build a web app for signing up to our school's open day and admissions events, where we list upcoming sessions with the date, time, location, and what each event covers, and parents or students can fill out a registration form right there on a desktop browser so we have everyone's details ahead of time.</v>
       </c>
       <c r="K320" t="str">
-        <v/>
+        <v>建立一个网站让人们可以报名参加学校的开放日和招生活动，列出即将举办的活动及其日期、时间、地点和内容，家长或学生可以在桌面浏览器上直接填写报名表单，这样我们可以提前收集所有人的信息。</v>
       </c>
       <c r="L320" t="str">
-        <v>[q_web_046_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="321">
@@ -12598,19 +12598,19 @@
         <v>medium</v>
       </c>
       <c r="H321">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I321">
-        <v>26335</v>
+        <v>0</v>
       </c>
       <c r="J321" t="str">
-        <v/>
+        <v>Need a web app that lets interested learners sign up for a free trial lesson, with a simple form asking for their name, contact info, and which subject they're interested in, plus a short section explaining what to expect in the trial — all on a single desktop browser page so people can read and register without bouncing around to different places.</v>
       </c>
       <c r="K321" t="str">
-        <v/>
+        <v>需要一个网站让有兴趣的学习者可以报名免费试课，包含一个简单的表单，询问名字、联系方式和感兴趣的科目，加上简短说明试课会是什么样——全部在单个桌面浏览器页面上，人们可以阅读并报名，无需在不同页面跳转。</v>
       </c>
       <c r="L321" t="str">
-        <v>[q_web_046_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="322">
@@ -12636,19 +12636,19 @@
         <v>medium</v>
       </c>
       <c r="H322">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I322">
-        <v>21510</v>
+        <v>0</v>
       </c>
       <c r="J322" t="str">
-        <v/>
+        <v>Make a website that highlights alumni career outcomes and real success stories from our graduates, with each person's name, the program they completed, where they work now, and a short quote or summary of how the course helped them, so prospective students browsing on a desktop browser can see concrete results before deciding to enroll.</v>
       </c>
       <c r="K322" t="str">
-        <v/>
+        <v>制作一个网站展示校友职业成就和真实成功故事，每个人显示名字、所学项目、现在的工作单位和关于课程如何帮助他们的短评或总结，这样潜在学生在桌面浏览器上可以看到具体成果，在决定报名前有参考。</v>
       </c>
       <c r="L322" t="str">
-        <v>[q_web_046_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="323">
@@ -12674,19 +12674,19 @@
         <v>medium</v>
       </c>
       <c r="H323">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I323">
-        <v>22334</v>
+        <v>0</v>
       </c>
       <c r="J323" t="str">
-        <v/>
+        <v>Create a web app for companies to inquire about our corporate training packages, where we list the different training programs we offer with descriptions and pricing ranges, and businesses can fill in a contact form saying what they need so we can send back a quote — all accessible from a desktop browser without back-and-forth emails just to get basic information.</v>
       </c>
       <c r="K323" t="str">
-        <v/>
+        <v>开发一个网站让企业可以咨询我们的企业培训套餐，列出我们提供的不同培训课程、描述和价格范围，企业可以填写表单说明需求这样我们可以回复报价——全部通过桌面浏览器访问，无需邮件来回就能获得基本信息。</v>
       </c>
       <c r="L323" t="str">
-        <v>[q_web_046_007] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="324">
@@ -12712,19 +12712,19 @@
         <v>medium</v>
       </c>
       <c r="H324">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I324">
-        <v>27424</v>
+        <v>0</v>
       </c>
       <c r="J324" t="str">
-        <v/>
+        <v>Need a web app where students can browse available courses and actually pay for the one they want without jumping through hoops — show me the course name, what it covers, the price, and a straightforward way to pay right there in the browser, so I stop losing people who just give up halfway through trying to figure out how to buy.</v>
       </c>
       <c r="K324" t="str">
-        <v/>
+        <v>需要一个网站让学生可以浏览课程并直接付费购买，不用费劲——显示课程名称、内容、价格和直接支付方式，这样我就不会再失去那些在搞不清楚怎么购买时放弃的用户。</v>
       </c>
       <c r="L324" t="str">
-        <v>[q_web_047_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="325">
@@ -12750,19 +12750,19 @@
         <v>medium</v>
       </c>
       <c r="H325">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I325">
-        <v>21624</v>
+        <v>0</v>
       </c>
       <c r="J325" t="str">
-        <v/>
+        <v>Need a web app for browsing and buying textbooks and school merchandise where I can search by course or grade level, see what's in stock, and add stuff to a cart without having to call anyone or dig through a wall of links — just a clean catalog with prices and a straightforward checkout flow.</v>
       </c>
       <c r="K325" t="str">
-        <v/>
+        <v>需要一个网站用来浏览和购买教科书和学校商品，可以按课程或年级搜索、查看库存，加入购物车，无需打电话或点击一堆链接——就是一个简洁的商品目录，有价格和直接的结账流程。</v>
       </c>
       <c r="L325" t="str">
-        <v>[q_web_047_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="326">
@@ -12788,19 +12788,19 @@
         <v>medium</v>
       </c>
       <c r="H326">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I326">
-        <v>54384</v>
+        <v>0</v>
       </c>
       <c r="J326" t="str">
-        <v/>
+        <v>Create a web app that handles buying certificates and credentials online, where you can browse available certificate types, pick the one you need, pay for it, and get a confirmation — all in one place so I don't have to email back and forth or figure out which office to contact.</v>
       </c>
       <c r="K326" t="str">
-        <v/>
+        <v>开发一个网站处理证书和凭证的在线购买，可以浏览可用的证书类型、选择需要的、付费并获得确认——全部在一个地方，我不用邮件往来或搞不清楚联系哪个部门。</v>
       </c>
       <c r="L326" t="str">
-        <v>[q_web_047_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="327">
@@ -12826,19 +12826,19 @@
         <v>medium</v>
       </c>
       <c r="H327">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="I327">
-        <v>26679</v>
+        <v>0</v>
       </c>
       <c r="J327" t="str">
-        <v/>
+        <v>A quote-and-customize tool for enterprise training packages that lives in the browser, where a company rep can pick the courses and seat counts they want, see the price update as they adjust things, and submit a request for a formal quote — saves so much back-and-forth compared to waiting on a sales rep to do it manually.</v>
       </c>
       <c r="K327" t="str">
-        <v/>
+        <v>一个浏览器内的企业培训套餐报价和定制工具，企业代表可以选择想要的课程和座位数、看到价格随调整实时更新、提交报价请求——比等销售代表手动处理省事得多。</v>
       </c>
       <c r="L327" t="str">
-        <v>[q_web_047_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="328">
@@ -12864,19 +12864,19 @@
         <v>medium</v>
       </c>
       <c r="H328">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="I328">
-        <v>23190</v>
+        <v>0</v>
       </c>
       <c r="J328" t="str">
-        <v/>
+        <v>Need a web app for HR managers to buy course seats in bulk, where you can search available courses, enter how many seats the team needs, see the total cost right away, and place the order — the whole thing should work in the browser so any HR person can handle it without needing IT to set something up.</v>
       </c>
       <c r="K328" t="str">
-        <v/>
+        <v>需要一个网站让人力资源经理可以批量购买课程座位，搜索可用课程、输入团队需要的座位数、立即看到总成本、下单——整个过程都在浏览器里进行，这样任何人力资源员工都可以处理，无需 IT 部门介入。</v>
       </c>
       <c r="L328" t="str">
-        <v>[q_web_047_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="329">
@@ -12902,19 +12902,19 @@
         <v>medium</v>
       </c>
       <c r="H329">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I329">
-        <v>28988</v>
+        <v>0</v>
       </c>
       <c r="J329" t="str">
-        <v/>
+        <v>A training ROI calculator for the web browser that lets managers plug in what they spent on corporate training and then see a report showing estimated returns and key numbers — the home screen of the app should have the input fields up top and the results laid out clearly below, so I can share it with leadership without having to explain a bunch of formulas myself.</v>
       </c>
       <c r="K329" t="str">
-        <v/>
+        <v>一个浏览器培训 ROI 计算器，让经理输入企业培训支出，然后看到显示预期回报和关键数字的报告——应用首页上面是输入框，下面清晰地显示结果，这样我可以和领导层分享，无需自己解释一堆公式。</v>
       </c>
       <c r="L329" t="str">
-        <v>[q_web_047_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="330">
@@ -12940,19 +12940,19 @@
         <v>medium</v>
       </c>
       <c r="H330">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I330">
-        <v>24935</v>
+        <v>0</v>
       </c>
       <c r="J330" t="str">
-        <v/>
+        <v>Need a web app for procurement teams to compare training vendors side by side, where you can filter by topic, price range, and delivery format, then pull up a comparison view showing ratings, features, and pricing — so we can stop keeping a giant spreadsheet just to decide which vendor to go with.</v>
       </c>
       <c r="K330" t="str">
-        <v/>
+        <v>需要一个网站让采购团队可以并排比较培训供应商，可以按主题、价格范围和授课形式筛选，然后查看显示评分、功能和定价的对比视图——这样我们就不用维护一个巨大的电子表格来决定选择哪个供应商。</v>
       </c>
       <c r="L330" t="str">
-        <v>[q_web_047_007] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="331">
@@ -12978,19 +12978,19 @@
         <v>medium</v>
       </c>
       <c r="H331">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I331">
-        <v>28607</v>
+        <v>0</v>
       </c>
       <c r="J331" t="str">
-        <v/>
+        <v>Need a web app for booking school open day visits, where you can see available dates on a calendar, pick a time slot, fill in your details, and get a confirmation email — something I can just open in my desktop browser and get done in a few minutes instead of waiting for someone to call me back.</v>
       </c>
       <c r="K331" t="str">
-        <v/>
+        <v>需要一个网站用来预订学校开放日参观，可以在日历上看到可用的日期、选择时间段、填写信息、获得确认邮件——我可以在桌面浏览器上直接完成，几分钟搞定，无需等待回电。</v>
       </c>
       <c r="L331" t="str">
-        <v>[q_web_048_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="332">
@@ -13016,19 +13016,19 @@
         <v>medium</v>
       </c>
       <c r="H332">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I332">
-        <v>28660</v>
+        <v>0</v>
       </c>
       <c r="J332" t="str">
-        <v/>
+        <v>Make a web app for booking a free trial lesson or a consultation session with a school or tutoring center, where you can pick the subject, choose a date and time that works, enter your contact info, and get a confirmation — the whole thing should be simple enough that any parent or student can use it in the browser without any fuss.</v>
       </c>
       <c r="K332" t="str">
-        <v/>
+        <v>开发一个网站预订免费试课或与学校或辅导中心的咨询会议，可以选择科目、选择合适的日期和时间、输入联系方式、获得确认——整个过程应该简单到任何家长或学生都可以在浏览器上使用，无需任何困难。</v>
       </c>
       <c r="L332" t="str">
-        <v>[q_web_048_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="333">
@@ -13054,19 +13054,19 @@
         <v>medium</v>
       </c>
       <c r="H333">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I333">
-        <v>20171</v>
+        <v>0</v>
       </c>
       <c r="J333" t="str">
-        <v/>
+        <v>Make a web app for scheduling admissions interviews, where applicants can log in, see available interview slots, pick one that fits their schedule, and get a reminder — the whole thing should run in the browser so students can book their slot from any computer instead of hunting down an email address to write to.</v>
       </c>
       <c r="K333" t="str">
-        <v/>
+        <v>开发一个网站用于预订招生面试，申请者可以登录、查看可用面试时间段、选择合适的、获得提醒——整个过程在浏览器里进行，这样学生可以从任何电脑预订，不用找邮箱地址去写信。</v>
       </c>
       <c r="L333" t="str">
-        <v>[q_web_048_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="334">
@@ -13092,19 +13092,19 @@
         <v>medium</v>
       </c>
       <c r="H334">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="I334">
-        <v>24658</v>
+        <v>0</v>
       </c>
       <c r="J334" t="str">
-        <v/>
+        <v>A booking tool for K-12 students to schedule one-on-one tutoring sessions, available in the browser on desktop, where you can browse tutor profiles by subject, see their open time slots on a weekly calendar, pick a session, and confirm the booking — parents should be able to see upcoming sessions and get reminders too.</v>
       </c>
       <c r="K334" t="str">
-        <v/>
+        <v>为 K-12 学生设计一个一对一辅导会话预订工具，在桌面浏览器上可用，可以按科目浏览导师档案、在周日历上看他们的开放时间段、选择会话、确认预订——家长也应该能看到即将进行的会话并获得提醒。</v>
       </c>
       <c r="L334" t="str">
-        <v>[q_web_048_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="335">
@@ -13130,19 +13130,19 @@
         <v>medium</v>
       </c>
       <c r="H335">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I335">
-        <v>23527</v>
+        <v>0</v>
       </c>
       <c r="J335" t="str">
-        <v/>
+        <v>Build a web app for reserving speaking practice slots at a language school, where students can see the week's available time slots, pick one that works, choose their preferred practice topic, and lock in their reservation — the site should work well in a desktop browser so the front desk can also see who has booked what at a glance.</v>
       </c>
       <c r="K335" t="str">
-        <v/>
+        <v>建立一个网站用于预订语言学校的口语练习时间段，学生可以看到本周可用的时间段、选择合适的、选择偏好的练习主题、锁定预约——网站应该在桌面浏览器上运行良好，这样前台也可以一目了然地看到谁预订了什么。</v>
       </c>
       <c r="L335" t="str">
-        <v>[q_web_048_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="336">
@@ -13168,19 +13168,19 @@
         <v>medium</v>
       </c>
       <c r="H336">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I336">
-        <v>25430</v>
+        <v>0</v>
       </c>
       <c r="J336" t="str">
-        <v/>
+        <v>Need a web app for finding and booking music lesson teachers, where you can filter by instrument and availability, see teacher profiles with short bios and hourly rates, pick a time slot on their calendar, and confirm the booking — so you stop the whole back-and-forth of texting five different teachers to check if they're free.</v>
       </c>
       <c r="K336" t="str">
-        <v/>
+        <v>需要一个网站用来寻找和预订音乐课教师，可以按乐器和可用性筛选、查看教师档案包含简介和时薪、在他们的日历上选择时间段、确认预订——这样就不用给五个不同的教师发短信问他们是否有空。</v>
       </c>
       <c r="L336" t="str">
-        <v>[q_web_048_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="337">
@@ -13206,19 +13206,19 @@
         <v>medium</v>
       </c>
       <c r="H337">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I337">
-        <v>24106</v>
+        <v>0</v>
       </c>
       <c r="J337" t="str">
-        <v/>
+        <v>Build a web app for booking university campus tours, where prospective students can pick a tour date, choose their preferred time slot, fill in a short form with their name and contact info, and get a confirmation — the app should also let the admissions office see all upcoming bookings in a list for the day so they can plan the tours properly.</v>
       </c>
       <c r="K337" t="str">
-        <v/>
+        <v>建立一个网站用于预订大学校园参观，潜在学生可以选择参观日期、选择偏好的时间段、填写包含名字和联系方式的简短表单、获得确认——应用还应该让招生办公室看到当日的所有预订列表，这样他们可以妥善规划参观。</v>
       </c>
       <c r="L337" t="str">
-        <v>[q_web_048_007] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="338">
@@ -13244,19 +13244,19 @@
         <v>medium</v>
       </c>
       <c r="H338">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I338">
-        <v>19413</v>
+        <v>0</v>
       </c>
       <c r="J338" t="str">
-        <v/>
+        <v>Need a web app for an online course platform where I can browse courses by topic, see the full list of lessons inside each one before I enroll, track which lessons I've completed, and pick up right where I left off — the kind of thing I can use in a desktop browser without having to dig through menus to find my progress.</v>
       </c>
       <c r="K338" t="str">
-        <v/>
+        <v>需要一个在线课程平台网站，可以按主题浏览课程、在报名前查看每个课程的完整课程列表、跟踪已完成的课程、从中断处继续——这种东西我可以在桌面浏览器上使用，无需翻找菜单来查找进度。</v>
       </c>
       <c r="L338" t="str">
-        <v>[q_web_049_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="339">
@@ -13282,19 +13282,19 @@
         <v>medium</v>
       </c>
       <c r="H339">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I339">
-        <v>25019</v>
+        <v>0</v>
       </c>
       <c r="J339" t="str">
-        <v/>
+        <v>An LMS-style learning management tool for the web browser that keeps all my enrolled courses in one list, lets me check off lessons as I finish them, and shows me a clear progress bar for each course — it should also let me take notes per lesson so I can keep everything organized in one place.</v>
       </c>
       <c r="K339" t="str">
-        <v/>
+        <v>一个浏览器的学习管理系统工具，把所有报名课程放在一个列表里、课程完成后勾选课程、为每个课程显示清晰的进度条——还应该让我为每堂课做笔记，这样可以在一个地方把所有内容整理好。</v>
       </c>
       <c r="L339" t="str">
-        <v>[q_web_049_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="340">
@@ -13320,19 +13320,19 @@
         <v>medium</v>
       </c>
       <c r="H340">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I340">
-        <v>24175</v>
+        <v>0</v>
       </c>
       <c r="J340" t="str">
-        <v/>
+        <v>A practice test tool for the browser where I can pick a subject, work through a set of questions one by one, see the right answer after each one, and get a score summary at the end — it should also let me save a list of questions I got wrong so I can review them again later.</v>
       </c>
       <c r="K340" t="str">
-        <v/>
+        <v>一个浏览器练习测试工具，可以选择科目、逐题做题、每题后看正确答案、最后获得分数总结——还应该让我保存答错的题目列表，之后可以再复习。</v>
       </c>
       <c r="L340" t="str">
-        <v>[q_web_049_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="341">
@@ -13358,19 +13358,19 @@
         <v>medium</v>
       </c>
       <c r="H341">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I341">
-        <v>32921</v>
+        <v>0</v>
       </c>
       <c r="J341" t="str">
-        <v/>
+        <v>Make a flashcard study app for the web browser that lets me create decks of cards, flip through them one at a time, mark which ones I know and which ones I need to review again, and then shows me the cards I struggled with more often — I want a simple list of all my decks on the home screen so I can jump into any one right away.</v>
       </c>
       <c r="K341" t="str">
-        <v/>
+        <v>做一个网站的闪卡学习应用，可以创建卡片组、逐张翻转、标记已掌握和需要复习的卡片、然后更频繁地复习不熟悉的卡片——我想在首页看到所有卡片组的简单列表，这样可以立即进入任何一个。</v>
       </c>
       <c r="L341" t="str">
-        <v>[q_web_049_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="342">
@@ -13396,19 +13396,19 @@
         <v>medium</v>
       </c>
       <c r="H342">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I342">
-        <v>22760</v>
+        <v>0</v>
       </c>
       <c r="J342" t="str">
-        <v/>
+        <v>Need a reading tracker for academic papers that works in the browser on desktop, where I can add papers to a list, mark my progress through each one, jot down short notes or highlights, and see at a glance which papers I've finished and which ones are still in progress — organized by topic so I can keep my research tidy.</v>
       </c>
       <c r="K342" t="str">
-        <v/>
+        <v>需要一个在桌面浏览器上的学术论文阅读追踪应用，可以添加论文到列表、标记每篇论文的阅读进度、记下简短的笔记或亮点、一目了然地看到已完成和进行中的论文——按主题组织，这样可以保持研究整洁。</v>
       </c>
       <c r="L342" t="str">
-        <v>[q_web_049_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="343">
@@ -13434,19 +13434,19 @@
         <v>medium</v>
       </c>
       <c r="H343">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I343">
-        <v>26129</v>
+        <v>0</v>
       </c>
       <c r="J343" t="str">
-        <v/>
+        <v>Make a study group planner app for the web browser where students can create a group for a specific course, list their available times for the week, and see where everyone's schedules overlap so it's easy to agree on a meeting time — the home screen of the app should show all active study groups and the next scheduled session for each one.</v>
       </c>
       <c r="K343" t="str">
-        <v/>
+        <v>做一个学习小组规划应用给浏览器，学生可以为特定课程创建小组、列出一周的可用时间、看到所有人日程重叠的位置这样很容易约定会议时间——应用首页应该显示所有活跃的学习小组和每个小组下次的预定会议。</v>
       </c>
       <c r="L343" t="str">
-        <v>[q_web_049_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="344">
@@ -13472,19 +13472,19 @@
         <v>medium</v>
       </c>
       <c r="H344">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I344">
-        <v>23512</v>
+        <v>0</v>
       </c>
       <c r="J344" t="str">
-        <v/>
+        <v>Need a vocabulary builder app for the web browser where I can look up words in a foreign language, save them to personal word lists by topic, and play back a short audio clip of a native speaker saying each word — I also want to see the word's definition and an example sentence right next to the audio so I can study everything at once.</v>
       </c>
       <c r="K344" t="str">
-        <v/>
+        <v>需要一个浏览器的词汇生成器应用，可以查询外语单词、按主题保存到个人词汇列表、播放本地使用者的发音短音频——我还想看到单词的定义和例句就在音频旁边，这样可以一次学习所有内容。</v>
       </c>
       <c r="L344" t="str">
-        <v>[q_web_049_007] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="345">
@@ -13510,19 +13510,19 @@
         <v>medium</v>
       </c>
       <c r="H345">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I345">
-        <v>24161</v>
+        <v>0</v>
       </c>
       <c r="J345" t="str">
-        <v/>
+        <v>Need a web app for an alumni network where graduates can create a profile with their graduation year, current job, and city, browse other alumni by industry or location, and send a quick message to reconnect — something that runs nicely in the desktop browser with a list view on the left and profile details on the right.</v>
       </c>
       <c r="K345" t="str">
-        <v/>
+        <v>需要一个校友网络网站，毕业生可以创建档案显示毕业年份、当前工作和城市、按行业或地点浏览其他校友、发送快速消息重新联系——这种东西在桌面浏览器上运行良好，左边列表视图、右边档案详情。</v>
       </c>
       <c r="L345" t="str">
-        <v>[q_web_050_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="346">
@@ -13548,19 +13548,19 @@
         <v>medium</v>
       </c>
       <c r="H346">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I346">
-        <v>21573</v>
+        <v>0</v>
       </c>
       <c r="J346" t="str">
-        <v/>
+        <v>Create a student community web app where students from the same school can post questions, share notes, and reply to each other, with posts organized by subject or class — the home screen of the app should show a feed of recent posts so it's easy to see what's going on without having to click through a bunch of categories.</v>
       </c>
       <c r="K346" t="str">
-        <v/>
+        <v>创建一个学生社区网站，同校学生可以提问、分享笔记、互相回复，按科目或班级组织帖子——应用首页应该显示最近帖子的信息流，这样很容易看到发生了什么，无需点击一堆分类。</v>
       </c>
       <c r="L346" t="str">
-        <v>[q_web_050_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="347">
@@ -13586,19 +13586,19 @@
         <v>medium</v>
       </c>
       <c r="H347">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I347">
-        <v>22518</v>
+        <v>0</v>
       </c>
       <c r="J347" t="str">
-        <v/>
+        <v>Create a parent communication web app where teachers can post class announcements, share homework reminders, and parents can reply or ask quick questions — it should work in the desktop browser and keep messages grouped by class so parents only see what's relevant to their own kid's class.</v>
       </c>
       <c r="K347" t="str">
-        <v/>
+        <v>创建一个家长沟通网站，教师可以发布班级公告、分享作业提醒、家长可以回复或快速提问——应该在桌面浏览器上运行，按班级分组消息，这样家长只看到与自己孩子班级相关的内容。</v>
       </c>
       <c r="L347" t="str">
-        <v>[q_web_050_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="348">
@@ -13624,19 +13624,19 @@
         <v>medium</v>
       </c>
       <c r="H348">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="I348">
-        <v>23075</v>
+        <v>0</v>
       </c>
       <c r="J348" t="str">
-        <v/>
+        <v>Build a peer tutoring marketplace web app for university students, where students who need help in a course can post a request and students who know the subject can respond with their rate and availability — the app should let both sides browse listings, send messages, and confirm a session right in the browser.</v>
       </c>
       <c r="K348" t="str">
-        <v/>
+        <v>建立一个大学生同伴辅导市场网站，需要帮助的学生可以发布请求、了解该科目的学生可以回复说出费率和可用性——应用应该让双方浏览列表、发送消息、在浏览器里直接确认会话。</v>
       </c>
       <c r="L348" t="str">
-        <v>[q_web_050_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="349">
@@ -13662,19 +13662,19 @@
         <v>medium</v>
       </c>
       <c r="H349">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I349">
-        <v>25021</v>
+        <v>0</v>
       </c>
       <c r="J349" t="str">
-        <v/>
+        <v>Build a study group finder web app for online learners where you can post what course you're taking and what times you're free, browse other learners looking for study partners in the same course, and send a message to form a group — the whole thing should work in the browser so anyone taking an online class can use it from their desktop.</v>
       </c>
       <c r="K349" t="str">
-        <v/>
+        <v>建立一个在线学习者的学习小组查找网站，可以发布你在学什么课程以及什么时间有空、浏览其他同样课程的学习者、发送消息组建小组——整个过程在浏览器里，这样参加在线课程的任何人都可以从桌面使用它。</v>
       </c>
       <c r="L349" t="str">
-        <v>[q_web_050_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="350">
@@ -13700,19 +13700,19 @@
         <v>medium</v>
       </c>
       <c r="H350">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="I350">
-        <v>19416</v>
+        <v>0</v>
       </c>
       <c r="J350" t="str">
-        <v/>
+        <v>Create a faculty mentorship matching tool as a web app where graduate students can browse professor profiles sorted by research area and teaching style, then send a short intro message to request a mentorship connection, and professors can accept or decline from their own side of the app — I want the whole thing to run in a desktop browser so both students and faculty can use it comfortably while doing other work.</v>
       </c>
       <c r="K350" t="str">
-        <v/>
+        <v>做一个师生匹配工具网页应用，让研究生可以浏览教授资料（按研究方向和教学风格排序），发送简短自我介绍申请师徒关系，教授可以在自己的界面选择接受或拒绝——整个应用要在桌面浏览器上运行，这样师生都能在处理其他工作的同时舒适地使用。</v>
       </c>
       <c r="L350" t="str">
-        <v>[q_web_050_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="351">
@@ -13738,19 +13738,19 @@
         <v>medium</v>
       </c>
       <c r="H351">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I351">
-        <v>24634</v>
+        <v>0</v>
       </c>
       <c r="J351" t="str">
-        <v/>
+        <v>Need a collaborative lecture note wiki for a web app where everyone in a course can jump in and add their notes from the same lecture, and all the contributions get organized by topic or date so it's easy to find what you missed — I want it to work well in a desktop browser so people can have it open on one side while they study or review.</v>
       </c>
       <c r="K351" t="str">
-        <v/>
+        <v>做一个课堂笔记协作wiki网页应用，让课程里的每个人都能跳进来给同一堂课添加笔记，所有内容按话题或日期整理，方便查找缺漏的部分——要在桌面浏览器上用得顺手，这样学生可以一边复习一边开着它。</v>
       </c>
       <c r="L351" t="str">
-        <v>[q_web_050_007] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="352">
@@ -13776,19 +13776,19 @@
         <v>medium</v>
       </c>
       <c r="H352">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I352">
-        <v>24351</v>
+        <v>0</v>
       </c>
       <c r="J352" t="str">
-        <v/>
+        <v>Make a student portal web app that pulls everything a student needs into one place — their class schedule, upcoming assignment deadlines, grades, and any school announcements — so I stop having to log into five different systems just to figure out what's due tomorrow, and it should work well in a desktop browser so I can keep it open while I'm doing homework.</v>
       </c>
       <c r="K352" t="str">
-        <v/>
+        <v>做一个学生门户网页应用，把学生需要的一切集中在一个地方——课程表、作业截止日期、成绩和学校公告——这样我就不用登五个不同的系统才能搞清楚明天要交什么，应该在桌面浏览器上用得顺手，这样我写作业的时候可以把它开着。</v>
       </c>
       <c r="L352" t="str">
-        <v>[q_web_051_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="353">
@@ -13814,19 +13814,19 @@
         <v>medium</v>
       </c>
       <c r="H353">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I353">
-        <v>26842</v>
+        <v>0</v>
       </c>
       <c r="J353" t="str">
-        <v/>
+        <v>Make a course selection and scheduling tool as a web app where students can see all the available classes for the semester laid out in a weekly grid, pick the ones they want, and instantly spot if there are any time conflicts — I'm tired of manually cross-checking everything, so having it all visible at once in a desktop browser would save a ton of headache.</v>
       </c>
       <c r="K353" t="str">
-        <v/>
+        <v>做一个选课和排课工具网页应用，学生可以看到学期里所有可选课程（用周视图显示），选中想上的，立刻看出是否有时间冲突——我不想再手动逐个对照，用桌面浏览器一眼全看到就能省很多麻烦。</v>
       </c>
       <c r="L353" t="str">
-        <v>[q_web_051_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="354">
@@ -13852,19 +13852,19 @@
         <v>medium</v>
       </c>
       <c r="H354">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I354">
-        <v>23393</v>
+        <v>0</v>
       </c>
       <c r="J354" t="str">
-        <v/>
+        <v>Create a web app for handling exams and homework submissions where students can see all their upcoming assignments and due dates in one list, click into each one to submit their work, and check their grade and any feedback once the teacher posts it — I want this to work from a desktop browser so it's easy to use while I'm sitting at my desk writing papers.</v>
       </c>
       <c r="K354" t="str">
-        <v/>
+        <v>做一个考试和作业提交网页应用，学生可以在一个列表里看所有待交作业和截止日期，点进去提交作业，查看老师批改后的成绩和反馈——要在桌面浏览器上用，这样坐在桌前写论文的时候方便使用。</v>
       </c>
       <c r="L354" t="str">
-        <v>[q_web_051_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="355">
@@ -13890,19 +13890,19 @@
         <v>medium</v>
       </c>
       <c r="H355">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="I355">
-        <v>23255</v>
+        <v>0</v>
       </c>
       <c r="J355" t="str">
-        <v/>
+        <v>Create a student attendance tracker web app for K-12 schools where teachers can mark each student present, absent, or late class by class, and at the end of the week or month the app shows a clear summary per student so nobody has to dig through notebooks or spreadsheets — it should run in a desktop browser so teachers can use it right from their desk between classes.</v>
       </c>
       <c r="K355" t="str">
-        <v/>
+        <v>做一个K-12学校学生出勤追踪网页应用，老师可以逐堂课标记学生出勤、缺勤或迟到，周末或月末时应用显示每个学生的统计摘要，不用翻笔记本或电子表格——应该在桌面浏览器上运行，老师课间在办公桌就能用。</v>
       </c>
       <c r="L355" t="str">
-        <v>[q_web_051_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="356">
@@ -13928,19 +13928,19 @@
         <v>medium</v>
       </c>
       <c r="H356">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="I356">
-        <v>26570</v>
+        <v>0</v>
       </c>
       <c r="J356" t="str">
-        <v/>
+        <v>Need a transcript request and verification tool as a web app where students can fill out a form to request their official academic transcript, choose where it gets sent, and then track the status of their request so they're not emailing the registrar every day asking if it went out yet — the whole thing should work in a desktop browser so it's easy to do between classes.</v>
       </c>
       <c r="K356" t="str">
-        <v/>
+        <v>做一个成绩单申请和核实网页应用，学生可以填表申请正式成绩单、选择寄送地址、追踪申请进度，这样就不用每天都给教务处发邮件问是否已寄出——整个应用在桌面浏览器上用，利用课间时间很方便。</v>
       </c>
       <c r="L356" t="str">
-        <v>[q_web_051_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="357">
@@ -13966,19 +13966,19 @@
         <v>medium</v>
       </c>
       <c r="H357">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I357">
-        <v>21853</v>
+        <v>0</v>
       </c>
       <c r="J357" t="str">
-        <v/>
+        <v>Create a lesson plan builder web app for teachers where you can write up a lesson with goals, activities, and materials, save it to your personal collection, and also browse a shared library of plans that other teachers in the school have uploaded — the idea is to stop starting from scratch every week, and it needs to work well in a desktop browser so teachers can use it on their classroom or office computer.</v>
       </c>
       <c r="K357" t="str">
-        <v/>
+        <v>做一个教案制作网页应用，老师可以写教案（包括目标、活动和教材），保存到个人收藏，还可以浏览学校其他老师上传的共享教案库——目的是别再每周从零开始做教案，应该在桌面浏览器上用得顺手，老师在教室或办公室的电脑上就能用。</v>
       </c>
       <c r="L357" t="str">
-        <v>[q_web_051_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="358">
@@ -14004,19 +14004,19 @@
         <v>medium</v>
       </c>
       <c r="H358">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="I358">
-        <v>24592</v>
+        <v>0</v>
       </c>
       <c r="J358" t="str">
-        <v/>
+        <v>Need a grading criteria builder as a web app where teachers can set up a rubric for any assignment by defining the categories being graded and what each score level means, then save it and reuse it across different classes — I want this to run in a desktop browser so I can have it open alongside whatever assignment I'm creating and fill it in as I go.</v>
       </c>
       <c r="K358" t="str">
-        <v/>
+        <v>做一个评分标准制作网页应用，老师可以为任何作业建立评分标准（定义评分维度和各分数段的含义），保存后能在不同班级复用——要在桌面浏览器上运行，这样我制作作业时可以同时开着，边设计边填。</v>
       </c>
       <c r="L358" t="str">
-        <v>[q_web_051_007] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="359">
@@ -14042,19 +14042,19 @@
         <v>medium</v>
       </c>
       <c r="H359">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I359">
-        <v>30602</v>
+        <v>0</v>
       </c>
       <c r="J359" t="str">
-        <v/>
+        <v>Create a personal author or editor homepage website that feels like flipping through a beautifully curated literary magazine — warm, editorial typography, a tasteful color palette, and the author's writing laid out with the kind of care you'd expect from a printed journal, with space to feature a bio, a selection of published pieces, and a way for readers to get in touch, all designed for desktop browsers where it can really breathe and make an impression.</v>
       </c>
       <c r="K359" t="str">
-        <v/>
+        <v>做一个作家或编辑个人主页网站，感觉像翻着精心策划的文学杂志——温暖的编辑式排版、考究的配色、写作作品精心呈现，有地方展示简历、代表作和读者联系方式，全在桌面浏览器上设计，让内容有充分的呼吸空间和视觉冲击。</v>
       </c>
       <c r="L359" t="str">
-        <v>[q_web_052_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="360">
@@ -14080,19 +14080,19 @@
         <v>medium</v>
       </c>
       <c r="H360">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I360">
-        <v>23483</v>
+        <v>0</v>
       </c>
       <c r="J360" t="str">
-        <v/>
+        <v>Need a web app that works as an awards archive showcasing a journalist's or publication's honors over the years — I want it to feel distinguished and understated, like a gallery wall done right, where each award gets its moment with the year, the category, and a little context, laid out so it reads elegantly in a desktop browser rather than feeling like a cluttered resume dump.</v>
       </c>
       <c r="K360" t="str">
-        <v/>
+        <v>做一个新闻工作者或媒体奖项档案库网页应用，展示多年来赢得的荣誉——要显得低调而精致，像一面布置妥当的陈列墙，每个奖项都有年份、类别和简短介绍，排版优雅地展现在桌面浏览器上，而不是简历式的堆砌。</v>
       </c>
       <c r="L360" t="str">
-        <v>[q_web_052_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="361">
@@ -14118,19 +14118,19 @@
         <v>medium</v>
       </c>
       <c r="H361">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I361">
-        <v>23713</v>
+        <v>0</v>
       </c>
       <c r="J361" t="str">
-        <v/>
+        <v>Create a brand centennial history web app that tells a hundred years of a company's story in a way that feels like an art book brought to life on screen — rich visuals, a sense of era for each decade, evocative writing woven in alongside archival imagery, and a timeline that you scroll through at your own pace on a desktop browser, letting the story unfold chapter by chapter in a way that feels genuinely worth reading.</v>
       </c>
       <c r="K361" t="str">
-        <v/>
+        <v>做一个品牌百年历史网页应用，讲述公司一百年的故事就像一本艺术品书呈现在屏幕上——丰富的视觉效果、每个年代的时代感、具有感染力的文字配合档案照片、用户可以在桌面浏览器上自主掌握浏览节奏，让故事一章一章展开，读起来真的值得。</v>
       </c>
       <c r="L361" t="str">
-        <v>[q_web_052_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="362">
@@ -14156,19 +14156,19 @@
         <v>medium</v>
       </c>
       <c r="H362">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="I362">
-        <v>21564</v>
+        <v>0</v>
       </c>
       <c r="J362" t="str">
-        <v/>
+        <v>Create a magazine cover archive gallery web app that lets you browse decades of iconic covers in a way that actually feels like flipping through a visual history — the covers should look gorgeous and large on a desktop browser, organized by era so you can drift from one decade to the next, and clicking on one should give you a closer look along with a bit of context about that issue's cultural moment.</v>
       </c>
       <c r="K362" t="str">
-        <v/>
+        <v>做一个杂志封面档案库网页应用，让你能浏览几十年的标志性封面，感觉像翻阅视觉历史——封面在桌面浏览器上应该看起来绚丽大气，按年代整理可以按十年流转，点开一个封面能看到更大的图和那期的文化背景。</v>
       </c>
       <c r="L362" t="str">
-        <v>[q_web_052_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="363">
@@ -14194,19 +14194,19 @@
         <v>medium</v>
       </c>
       <c r="H363">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I363">
-        <v>26624</v>
+        <v>0</v>
       </c>
       <c r="J363" t="str">
-        <v/>
+        <v>Build a newspaper historical front page browser app that lets you scroll back through decades of front pages from a single publication, feeling like you're actually stepping into each era — the typography and layout of each page should be faithfully displayed on a desktop browser, with a way to filter by year or major event so readers can trace how the paper covered different moments in history over time.</v>
       </c>
       <c r="K363" t="str">
-        <v/>
+        <v>做一个报纸历史头版浏览器网页应用，让你能往后翻阅几十年的报纸头版，感觉像真的走进了不同的时代——每一页的排版和字体应该在桌面浏览器上真实再现，能按年份或重大事件筛选，这样读者可以追踪报纸在历史上如何报道不同事件。</v>
       </c>
       <c r="L363" t="str">
-        <v>[q_web_052_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="364">
@@ -14232,19 +14232,19 @@
         <v>medium</v>
       </c>
       <c r="H364">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="I364">
-        <v>22312</v>
+        <v>0</v>
       </c>
       <c r="J364" t="str">
-        <v/>
+        <v>Need a publishing house book catalog web app that feels like browsing a beautifully designed bookshop rather than a plain product list — each title gets its cover, a bit of descriptive copy, and a sense of the publisher's taste, organized in a way that's easy to explore by genre or year, and the whole thing should look stunning in a desktop browser where you can really appreciate the cover art and editorial curation.</v>
       </c>
       <c r="K364" t="str">
-        <v/>
+        <v>做一个出版社图书目录网页应用，感觉像逛设计精良的书店而不是看平庸的产品列表——每本书都有封面、简介和出版社的品味体现，按类型或年份组织，在桌面浏览器上看起来精致，能充分欣赏封面艺术和编辑的审美。</v>
       </c>
       <c r="L364" t="str">
-        <v>[q_web_052_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="365">
@@ -14270,19 +14270,19 @@
         <v>medium</v>
       </c>
       <c r="H365">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I365">
-        <v>25880</v>
+        <v>0</v>
       </c>
       <c r="J365" t="str">
-        <v/>
+        <v>Make a literary journal back-issue archive browser as a web app where readers can explore past issues of a journal with a look that feels true to its print heritage — elegant, understated, easy to navigate issue by issue in a desktop browser — with each issue showing the cover, a list of contributors and pieces inside, and a way to dig into any particular essay or poem that catches your eye.</v>
       </c>
       <c r="K365" t="str">
-        <v/>
+        <v>做一个文学期刊往期档案浏览网页应用，读者可以浏览期刊的过往期数，设计风格贴近其印刷版的气质——雅致克制、容易按期浏览、在桌面浏览器上好用——每期显示封面、目录和作者名单，能深入浏览任何吸引你的文章或诗歌。</v>
       </c>
       <c r="L365" t="str">
-        <v>[q_web_052_007] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="366">
@@ -14308,19 +14308,19 @@
         <v>medium</v>
       </c>
       <c r="H366">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I366">
-        <v>20700</v>
+        <v>0</v>
       </c>
       <c r="J366" t="str">
-        <v/>
+        <v>Make a news portal web app that feels like the front page of a really well-designed broadsheet brought into the browser — clean editorial hierarchy, clear sections for different topics, headline stories given proper visual weight, and a reading experience on desktop that actually makes you want to stay and read rather than just skim headlines and bounce.</v>
       </c>
       <c r="K366" t="str">
-        <v/>
+        <v>做一个新闻门户网页应用，感觉像一份设计精良的大报的头版搬进了浏览器——清晰的编辑层级、不同话题的分栏、重要新闻有视觉权重、在桌面阅读时确实让人想停下来仔细读，而不是只是浏览标题然后离开。</v>
       </c>
       <c r="L366" t="str">
-        <v>[q_web_053_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="367">
@@ -14346,19 +14346,19 @@
         <v>medium</v>
       </c>
       <c r="H367">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="I367">
-        <v>22858</v>
+        <v>0</v>
       </c>
       <c r="J367" t="str">
-        <v/>
+        <v>Make an online magazine web app that captures the feeling of flipping through a beautifully art-directed print publication on a desktop browser — rich full-bleed imagery for lead stories, considered typography that varies across sections to give each one its own personality, and a layout that rewards browsing so readers linger rather than just land and leave.</v>
       </c>
       <c r="K367" t="str">
-        <v/>
+        <v>做一个在线杂志网页应用，捕捉翻阅精心艺术指导的印刷杂志的感觉，在桌面浏览器上呈现——重要故事有满屏背景图片、不同栏目的排版各具特色彰显个性、版式鼓励浏览让读者愿意停留而非仓促离开。</v>
       </c>
       <c r="L367" t="str">
-        <v>[q_web_053_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="368">
@@ -14384,19 +14384,19 @@
         <v>medium</v>
       </c>
       <c r="H368">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I368">
-        <v>21324</v>
+        <v>0</v>
       </c>
       <c r="J368" t="str">
-        <v/>
+        <v>Build a feature writing and longform column app for a website where in-depth reported stories get the visual space and editorial care they deserve — immersive full-screen opening images, generous line spacing that makes long reads comfortable on a desktop browser, a clean sidebar that shows related pieces without feeling cluttered, and a quiet, focused vibe that puts the writing front and center.</v>
       </c>
       <c r="K368" t="str">
-        <v/>
+        <v>做一个深度报道和专栏文章网页应用，让深度调查报道能获得应有的视觉空间和编辑关怀——沉浸式的全屏开头图片、慷慨的行距让长篇阅读在桌面浏览器上舒适、简洁侧栏显示相关文章不显得杂乱、安静专注的风格让写作成为中心。</v>
       </c>
       <c r="L368" t="str">
-        <v>[q_web_053_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="369">
@@ -14422,19 +14422,19 @@
         <v>medium</v>
       </c>
       <c r="H369">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I369">
-        <v>21210</v>
+        <v>0</v>
       </c>
       <c r="J369" t="str">
-        <v/>
+        <v>Create a podcast show website as a web app that has the warm, inviting feel of a late-night radio station translated into beautiful web design — the kind of place where browsing episodes in a desktop browser feels like discovering a curated music shop, with rich show art, episode descriptions that actually make you want to listen, and a player that stays present as you browse through the archive.</v>
       </c>
       <c r="K369" t="str">
-        <v/>
+        <v>做一个播客节目网站网页应用，具有深夜电台的温暖邀请感，翻译成精美的网页设计——在桌面浏览器浏览节目就像发现精选音乐小店、节目有精美的封面、剧集描述让人想听、播放器始终可用当你浏览档案。</v>
       </c>
       <c r="L369" t="str">
-        <v>[q_web_053_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="370">
@@ -14460,19 +14460,19 @@
         <v>medium</v>
       </c>
       <c r="H370">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I370">
-        <v>19255</v>
+        <v>0</v>
       </c>
       <c r="J370" t="str">
-        <v/>
+        <v>Make an e-journal web app that reads and feels like a premium academic or cultural publication in digital form — clean typographic layouts with enough whitespace to breathe, organized by issue and section so readers can navigate in a desktop browser the way you'd naturally flip through a printed journal, and a visual presentation that makes even dense scholarly content feel considered and worth reading.</v>
       </c>
       <c r="K370" t="str">
-        <v/>
+        <v>做一个电子期刊网页应用，读起来和感觉都像高级学术或文化数字出版物——排版整洁有充分的留白，按期和栏目组织让读者在桌面浏览器上自然地翻阅，视觉呈现让即使晦涩的学术内容也显得经过精心考虑值得一读。</v>
       </c>
       <c r="L370" t="str">
-        <v>[q_web_053_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="371">
@@ -14498,19 +14498,19 @@
         <v>medium</v>
       </c>
       <c r="H371">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I371">
-        <v>20589</v>
+        <v>0</v>
       </c>
       <c r="J371" t="str">
-        <v/>
+        <v>Build a long-form investigative journalism app as a website that gives local reporting the same visual gravitas you'd expect from a major national outlet — deep, immersive story layouts with full-bleed photography, clear navigation so desktop browser readers can move between investigations and follow a reporter's body of work, and a tone that feels serious and trustworthy rather than sensational.</v>
       </c>
       <c r="K371" t="str">
-        <v/>
+        <v>做一个深度调查性新闻网页应用，给地方报道赋予国家级大媒体应有的视觉分量——沉浸式故事版式、满屏摄影、清晰导航让桌面浏览器读者能在调查间切换并追踪记者的工作、气调专业可信而非耸人听闻。</v>
       </c>
       <c r="L371" t="str">
-        <v>[q_web_053_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="372">
@@ -14536,19 +14536,19 @@
         <v>medium</v>
       </c>
       <c r="H372">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I372">
-        <v>20362</v>
+        <v>0</v>
       </c>
       <c r="J372" t="str">
-        <v/>
+        <v>Create a digital photo essay and photojournalism publication as a web app where every story is presented like a considered exhibition — full-width photographs that command attention in a desktop browser, minimal text laid in cleanly alongside the images so the visuals do the heavy lifting, and a browsing experience that feels more like walking through a gallery than scrolling a feed.</v>
       </c>
       <c r="K372" t="str">
-        <v/>
+        <v>做一个数字摄影随笔和新闻摄影出版网页应用，每个故事都像精心策划的展览呈现——全宽摄影在桌面浏览器抓住注意力、简洁文字贴在图旁让视觉做主要工作、浏览体验更像在美术馆漫步而非刷信息流。</v>
       </c>
       <c r="L372" t="str">
-        <v>[q_web_053_007] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="373">
@@ -14574,19 +14574,19 @@
         <v>medium</v>
       </c>
       <c r="H373">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="I373">
-        <v>22630</v>
+        <v>0</v>
       </c>
       <c r="J373" t="str">
-        <v/>
+        <v>Create a subscription paywall web app for a publication that feels elegant and inviting rather than like a hard stop — the kind of experience in a desktop browser where you're given a genuine taste of the content and the reasons to subscribe feel compelling and beautifully presented, with clear tiers that show what each level of access includes and a signup flow that feels as refined as the publication itself.</v>
       </c>
       <c r="K373" t="str">
-        <v/>
+        <v>做一个订阅付费墙网页应用，感觉优雅邀请而不是生硬的阻挡——在桌面浏览器上应该给读者真实的内容品味和令人信服的订阅理由（精美呈现）、清晰的等级显示各档次包含内容、注册流程和刊物本身一样精细。</v>
       </c>
       <c r="L373" t="str">
-        <v>[q_web_054_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="374">
@@ -14612,19 +14612,19 @@
         <v>medium</v>
       </c>
       <c r="H374">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="I374">
-        <v>20894</v>
+        <v>0</v>
       </c>
       <c r="J374" t="str">
-        <v/>
+        <v>Build a membership website app that has the sophisticated warmth of a private reading club — the kind of place on a desktop browser where each membership tier feels genuinely special and the benefits are laid out in a way that communicates exclusivity and community at the same time, with the visual language of the page doing as much work as the copy to make joining feel like a meaningful thing worth doing.</v>
       </c>
       <c r="K374" t="str">
-        <v/>
+        <v>做一个会员网站应用，具有私人读书俱乐部的精致温暖——在桌面浏览器上这样的地方每个会员等级都感觉真正特殊、福利以传达排他性和社群感兼具的方式列出、页面的视觉语言和文案一样用力让加入感觉有意义值得去做。</v>
       </c>
       <c r="L374" t="str">
-        <v>[q_web_054_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="375">
@@ -14650,19 +14650,19 @@
         <v>medium</v>
       </c>
       <c r="H375">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="I375">
-        <v>20504</v>
+        <v>0</v>
       </c>
       <c r="J375" t="str">
-        <v/>
+        <v>Make a promotional event announcement app for the web — the kind that feels like opening a beautifully curated magazine spread, with a full-bleed hero image that sets the mood right away, warm typography that draws you in, and a color palette that matches the event's energy rather than looking like a generic flyer template, all viewable in a desktop browser where you can really appreciate the atmosphere.</v>
       </c>
       <c r="K375" t="str">
-        <v/>
+        <v>做一个宣传活动公告网页应用——感觉像打开精心策划的杂志跨页、全屏英雄图片立即烘托氛围、温暖排版吸引注意、配色符合活动能量而非泛用模板、在桌面浏览器上能充分欣赏这份气氛。</v>
       </c>
       <c r="L375" t="str">
-        <v>[q_web_054_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="376">
@@ -14688,19 +14688,19 @@
         <v>medium</v>
       </c>
       <c r="H376">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I376">
-        <v>20169</v>
+        <v>0</v>
       </c>
       <c r="J376" t="str">
-        <v/>
+        <v>Create a digital magazine sign-up tool that lives in the browser and feels as refined as the publication itself — the kind of web app where the cover art breathes, the subscription pitch reads like editorial copy rather than a sales form, and visitors are gently invited to leave their email through a layout that feels like flipping into a beautifully printed issue, with a lead-capture area that feels warm and tasteful rather than pushy.</v>
       </c>
       <c r="K376" t="str">
-        <v/>
+        <v>做一个数字杂志注册工具，在浏览器里就和刊物本身一样精细——网页应用里封面有充分呼吸空间、订阅宣传读起来像编辑文案而非销售表单、访客通过优雅的版式被温柔吸引留下邮箱（就像翻开印刷版一样）、注册区域温暖有品味而不是强硬推销。</v>
       </c>
       <c r="L376" t="str">
-        <v>[q_web_054_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="377">
@@ -14726,19 +14726,19 @@
         <v>medium</v>
       </c>
       <c r="H377">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="I377">
-        <v>21009</v>
+        <v>0</v>
       </c>
       <c r="J377" t="str">
-        <v/>
+        <v>Create a media kit showcase tool for desktop browsers that feels like a premium brand lookbook — the kind of web app where each advertising package is presented with its own visual identity, the numbers are styled so they read as editorial highlights rather than a rate card, and the whole experience has the kind of quiet confidence you'd expect from a publication that takes its design seriously, with a contact area that feels like an invitation rather than a form.</v>
       </c>
       <c r="K377" t="str">
-        <v/>
+        <v>做一个媒体资料包展示工具，在桌面浏览器上感觉像高端品牌产品手册——网页应用里每个广告位都有自己的视觉身份、数字排版得像编辑亮点而非报价单、整体氛围有认真对待设计的出版社应有的克制自信、联系区域像邀请而非表单。</v>
       </c>
       <c r="L377" t="str">
-        <v>[q_web_054_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="378">
@@ -14764,19 +14764,19 @@
         <v>medium</v>
       </c>
       <c r="H378">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I378">
-        <v>22766</v>
+        <v>0</v>
       </c>
       <c r="J378" t="str">
-        <v/>
+        <v>A podcast network growth campaign app for the browser that has that charged, electric energy of a concert poster crossed with an indie magazine — bold type that fills the screen on desktop, episode previews that feel curated rather than dumped in a list, and a sign-up moment that lands like the finale of a great show rather than a generic newsletter prompt, the whole vibe pulling people in because it just looks and feels alive.</v>
       </c>
       <c r="K378" t="str">
-        <v/>
+        <v>做一个播客网络增长宣传网页应用，具有演唱会海报搭配独立杂志的带电感——桌面屏幕上粗大字体填满空间、剧集预告感觉策划周密而非简单列表、注册时刻像伟大演出的高潮而非一般新闻通讯提示、整体氛围生动吸引人因为看起来和感觉都充满活力。</v>
       </c>
       <c r="L378" t="str">
-        <v>[q_web_054_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="379">
@@ -14802,19 +14802,19 @@
         <v>medium</v>
       </c>
       <c r="H379">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I379">
-        <v>20941</v>
+        <v>0</v>
       </c>
       <c r="J379" t="str">
-        <v/>
+        <v>A seasonal book bundle deals app for desktop browsers that feels like walking into a beautifully arranged indie bookshop — each bundle has its own little mood, like a hand-lettered gift tag and a cover arrangement that actually looks considered, with the seasonal theme bleeding through the colors and textures so autumn deals feel warm and winter deals feel cozy, and the whole browsing experience has the unhurried pace of someone who genuinely loves books.</v>
       </c>
       <c r="K379" t="str">
-        <v/>
+        <v>做一个季节书籍优惠包网页应用，在桌面浏览器上感觉像走进布置精良的独立书店——每个优惠包都有自己的小气氛（像手写礼签一样）、封面搭配显得经过考虑、季节主题透过配色和质感渗透进来（秋季交易温暖，冬季交易舒适）、整个浏览体验像真爱书的人那样不匆忙。</v>
       </c>
       <c r="L379" t="str">
-        <v>[q_web_054_007] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="380">
@@ -14840,19 +14840,19 @@
         <v>medium</v>
       </c>
       <c r="H380">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="I380">
-        <v>18963</v>
+        <v>0</v>
       </c>
       <c r="J380" t="str">
-        <v/>
+        <v>Make a paid subscription manager web app that finally takes the guesswork out of keeping track of which plan I'm on, when I get billed next, and what I actually get access to — I want to see all my subscription tiers in one place in a desktop browser, be able to upgrade or cancel without digging through five different settings screens, and get a clear reminder before any charge hits.</v>
       </c>
       <c r="K380" t="str">
-        <v/>
+        <v>做一个付费订阅管理网页应用，终于能不用猜测我订的什么计划、什么时候扣款、能用什么权限——在一个桌面浏览器界面集中看所有订阅等级、能升级或取消而不用在五个设置界面里钻来钻去、在任何扣款前收到清晰提醒。</v>
       </c>
       <c r="L380" t="str">
-        <v>[q_web_055_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="381">
@@ -14878,19 +14878,19 @@
         <v>medium</v>
       </c>
       <c r="H381">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I381">
-        <v>20107</v>
+        <v>0</v>
       </c>
       <c r="J381" t="str">
-        <v/>
+        <v>Build a book and merch buying app for the web where I can browse titles and cultural goods without losing my place every time I want to check the details on something — I want a clean list I can filter by type or topic, a simple way to add things to a cart, and a checkout that doesn't make me re-enter my address three times, all usable from a desktop browser.</v>
       </c>
       <c r="K381" t="str">
-        <v/>
+        <v>做一个书籍和文化周边购物网页应用，能浏览图书和文创商品而不用每次查详情就失去位置——清爽的列表、可按类型或话题筛选、简单加购物车方式、结账不用重复输三遍地址，全在桌面浏览器上用。</v>
       </c>
       <c r="L381" t="str">
-        <v>[q_web_055_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="382">
@@ -14916,19 +14916,19 @@
         <v>medium</v>
       </c>
       <c r="H382">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I382">
-        <v>18545</v>
+        <v>0</v>
       </c>
       <c r="J382" t="str">
-        <v/>
+        <v>Make a tipping and support tool as a web app where readers can quickly send a one-time or recurring contribution to a creator without going through a whole payment saga — I want preset amounts people can click, a simple way to leave a short note, and a confirmation that actually shows up right away so nobody wonders if it went through, all working smoothly in a desktop browser.</v>
       </c>
       <c r="K382" t="str">
-        <v/>
+        <v>做一个打赏和支持工具网页应用，让读者能快速一次性或定期给创作者打赏，不用经历整个付款流程——预设金额能直接点击、简单留言框、确认立即显示这样谁也不会怀疑是否成功，全在桌面浏览器顺畅运行。</v>
       </c>
       <c r="L382" t="str">
-        <v>[q_web_055_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="383">
@@ -14954,19 +14954,19 @@
         <v>medium</v>
       </c>
       <c r="H383">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="I383">
-        <v>20124</v>
+        <v>0</v>
       </c>
       <c r="J383" t="str">
-        <v/>
+        <v>Make a digital magazine subscription manager as a web app where I can see all the publications I'm subscribed to in one place, switch between monthly and annual billing without having to email support, and actually find the button to pause or cancel a subscription without it being buried — I want this to work cleanly in a desktop browser so I can handle everything in one sitting.</v>
       </c>
       <c r="K383" t="str">
-        <v/>
+        <v>做一个数字杂志订阅管理网页应用，能在一个地方看所有订阅的刊物、无需邮件支持直接在月付和年付间切换、能找到暂停或取消订阅按钮而不用层层翻找——在桌面浏览器上简洁运行这样一坐就能搞定所有事。</v>
       </c>
       <c r="L383" t="str">
-        <v>[q_web_055_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="384">
@@ -14992,19 +14992,19 @@
         <v>medium</v>
       </c>
       <c r="H384">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I384">
-        <v>16109</v>
+        <v>0</v>
       </c>
       <c r="J384" t="str">
-        <v/>
+        <v>Build a press release distribution tool as a web app where a brand can write up an announcement, pick which outlets or categories to send it to from a pre-loaded list, and submit it all in one go from a desktop browser without having to track down contact emails separately or manually follow up on every send — I want a simple tracker showing which outlets have picked it up.</v>
       </c>
       <c r="K384" t="str">
-        <v/>
+        <v>做一个新闻稿发布工具网页应用，品牌能写好公告、从预加载列表中选择要发到哪些媒体或分类、一次性提交，全在桌面浏览器完成而不用单独找联系邮箱或手动逐个跟进——要有简单的追踪器显示哪些媒体已刊登。</v>
       </c>
       <c r="L384" t="str">
-        <v>[q_web_055_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="385">
@@ -15030,19 +15030,19 @@
         <v>medium</v>
       </c>
       <c r="H385">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I385">
-        <v>20674</v>
+        <v>0</v>
       </c>
       <c r="J385" t="str">
-        <v/>
+        <v>Make a sponsored content marketplace tool as a web app where publishers can list their available placement spots and brands can browse and book them directly from a desktop browser — I want publishers to be able to set their rates and available dates, and brands to be able to send a request and get a confirmation without the whole thing turning into a back-and-forth email chain.</v>
       </c>
       <c r="K385" t="str">
-        <v/>
+        <v>做一个赞助内容市场工具网页应用，出版社能列出可用广告位置、品牌能在桌面浏览器直接浏览和预订——出版社能设定报价和可用日期，品牌能发请求并确认而不用陷入冗长邮件往来。</v>
       </c>
       <c r="L385" t="str">
-        <v>[q_web_055_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="386">
@@ -15068,19 +15068,19 @@
         <v>medium</v>
       </c>
       <c r="H386">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I386">
-        <v>20638</v>
+        <v>0</v>
       </c>
       <c r="J386" t="str">
-        <v/>
+        <v>An editorial content licensing tool for desktop browsers where I can upload an article or piece of creative work, set what kind of use I'm allowing and for how long, and have buyers request a license from the same place — a web app that keeps all the agreements in one spot so I'm not digging through inboxes trying to figure out who licensed what and when it expires.</v>
       </c>
       <c r="K386" t="str">
-        <v/>
+        <v>做一个编辑内容版权许可工具，在桌面浏览器上用——你能上传文章或创意作品、设定允许什么使用方式和多久、买家能从同一地方请求许可——网页应用把所有协议集中在一个地方这样我不用翻邮箱找谁许可了什么和何时过期。</v>
       </c>
       <c r="L386" t="str">
-        <v>[q_web_055_007] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="387">
@@ -15106,19 +15106,19 @@
         <v>medium</v>
       </c>
       <c r="H387">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I387">
-        <v>19626</v>
+        <v>0</v>
       </c>
       <c r="J387" t="str">
-        <v/>
+        <v>Make an interview scheduling tool as a web app where a journalist or reporter can see a person's available slots, pick a time, fill in a short topic brief, and get a confirmation without any back-and-forth — I want the whole thing usable from a desktop browser so I can book and manage all my upcoming interviews in one place instead of juggling emails.</v>
       </c>
       <c r="K387" t="str">
-        <v/>
+        <v>做一个采访预约工具网页应用，记者或采访者能看到受采访人的可用时间、选择时间、填简短话题摘要并得到确认，全无往来邮件——整个应用在桌面浏览器可用这样我能在一个地方预约和管理所有采访而不用在邮件里切换。</v>
       </c>
       <c r="L387" t="str">
-        <v>[q_web_056_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="388">
@@ -15144,19 +15144,19 @@
         <v>medium</v>
       </c>
       <c r="H388">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I388">
-        <v>20982</v>
+        <v>0</v>
       </c>
       <c r="J388" t="str">
-        <v/>
+        <v>Make a press conference seat reservation tool as a web app where credentialed journalists can log in, see which events are coming up, grab a seat for the ones they plan to cover, and get a reminder with the details before it starts — all manageable from a desktop browser so I'm not hunting through email threads to figure out if my spot is confirmed.</v>
       </c>
       <c r="K388" t="str">
-        <v/>
+        <v>做一个记者会座位预留工具网页应用，有证件的记者能登录、看即将来临的活动、为想报道的活动抢座位、在开始前收到详情提醒——全在桌面浏览器上管理这样我不用在邮件线索里翻找确认自己的座位。</v>
       </c>
       <c r="L388" t="str">
-        <v>[q_web_056_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="389">
@@ -15182,19 +15182,19 @@
         <v>medium</v>
       </c>
       <c r="H389">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I389">
-        <v>19534</v>
+        <v>0</v>
       </c>
       <c r="J389" t="str">
-        <v/>
+        <v>Create a book signing event registration tool as a web app where fans can browse upcoming signing events by author or date, pick a time slot that works for them, and get a confirmation with all the details right away — I want this to work smoothly in a desktop browser so readers can lock in their spot without having to call a bookstore or wait on a reply.</v>
       </c>
       <c r="K389" t="str">
-        <v/>
+        <v>做一个签售会注册工具网页应用，粉丝能浏览按作者或日期排列的即将签售活动、选择合适的时间档、立刻得到包含详情的确认——在桌面浏览器上顺畅运行这样读者能直接锁定座位而不用打电话给书店或等回复。</v>
       </c>
       <c r="L389" t="str">
-        <v>[q_web_056_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="390">
@@ -15220,19 +15220,19 @@
         <v>medium</v>
       </c>
       <c r="H390">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I390">
-        <v>20930</v>
+        <v>0</v>
       </c>
       <c r="J390" t="str">
-        <v/>
+        <v>Need a slot booking tool as a web app where literary festival attendees can browse which authors are available for a meet-and-greet, pick an open time from a simple calendar view in their desktop browser, and register their spot with just their name and email — I want a confirmation sent immediately so people actually show up at the right time.</v>
       </c>
       <c r="K390" t="str">
-        <v/>
+        <v>做一个档期预约工具网页应用，文学节参与者能浏览哪些作者提供见面会、从桌面浏览器的简单日历视图选择开放的时间、只用名字和邮箱注册座位——立刻发确认这样人们确实会在对的时间出现。</v>
       </c>
       <c r="L390" t="str">
-        <v>[q_web_056_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="391">
@@ -15258,19 +15258,19 @@
         <v>medium</v>
       </c>
       <c r="H391">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I391">
-        <v>17030</v>
+        <v>0</v>
       </c>
       <c r="J391" t="str">
-        <v/>
+        <v>Create a podcast guest booking tool as a web app where aspiring guests can submit a short pitch with their topic and bio, and hosts can review all the incoming requests in one place from a desktop browser, accept or pass on each one, and have the recording time slot automatically offered to accepted guests — so the whole process stops living in scattered inboxes.</v>
       </c>
       <c r="K391" t="str">
-        <v/>
+        <v>做一个播客嘉宾预约工具网页应用，有意参与的嘉宾能提交简短宣传（包含话题和简历），主播能在桌面浏览器在一个地方审看所有来稿、接受或拒绝、系统自动把录制档期提给被接受的嘉宾——这样整个流程就不会散落在各个邮箱里。</v>
       </c>
       <c r="L391" t="str">
-        <v>[q_web_056_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="392">
@@ -15296,19 +15296,19 @@
         <v>medium</v>
       </c>
       <c r="H392">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I392">
-        <v>19893</v>
+        <v>0</v>
       </c>
       <c r="J392" t="str">
-        <v/>
+        <v>Make a media credentials application tool as a web app where journalists can fill out their press pass request, upload their ID or outlet info, and pick a pickup time slot from the available options — all handled through a desktop browser so the whole credentials process is in one place and I'm not chasing down confirmation emails or showing up at the wrong window.</v>
       </c>
       <c r="K392" t="str">
-        <v/>
+        <v>做一个记者证申请工具网页应用，记者能填写提交传播证申请、上传身份证或媒体证件、从可用选项选择取件档期——全在桌面浏览器通过这样整个申证流程集中在一个地方、我不用追确认邮件或去错的窗口。</v>
       </c>
       <c r="L392" t="str">
-        <v>[q_web_056_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="393">
@@ -15334,19 +15334,19 @@
         <v>medium</v>
       </c>
       <c r="H393">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="I393">
-        <v>18023</v>
+        <v>0</v>
       </c>
       <c r="J393" t="str">
-        <v/>
+        <v>Create a newsroom tour booking tool as a web app where journalism students can browse available tour dates, pick a group time slot that fits their schedule, and register their spot in one go from a desktop browser — I want a clear confirmation page with all the visit details so nobody shows up on the wrong day or has to call to check if they're signed up.</v>
       </c>
       <c r="K393" t="str">
-        <v/>
+        <v>做一个新闻社参观预约工具网页应用，新闻系学生能浏览可用参观日期、为符合日程的集体参观时间选择档期、一次性在桌面浏览器注册——清晰的确认页显示访问细节这样没人会搞错日期或需要打电话确认自己是否报了名。</v>
       </c>
       <c r="L393" t="str">
-        <v>[q_web_056_007] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="394">
@@ -15372,19 +15372,19 @@
         <v>medium</v>
       </c>
       <c r="H394">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I394">
-        <v>19912</v>
+        <v>0</v>
       </c>
       <c r="J394" t="str">
-        <v/>
+        <v>Make a knowledge topic site app for the browser where articles and explainers are organized by theme so you can actually follow a subject from start to finish — I want each topic to have its own section with the pieces listed in a logical reading order, a way to mark what I've already read, and a search so I can find a specific piece without scrolling through everything, all working nicely on a desktop.</v>
       </c>
       <c r="K394" t="str">
-        <v/>
+        <v>做一个知识专题网站应用，文章和讲解按主题组织这样你能从头到尾跟踪一个专题——每个专题有自己的栏目文章按合理阅读顺序列出、能标记已读内容、搜索功能能让我找特定文章而不用滚遍所有内容，在桌面上运行顺畅。</v>
       </c>
       <c r="L394" t="str">
-        <v>[q_web_057_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="395">
@@ -15410,19 +15410,19 @@
         <v>medium</v>
       </c>
       <c r="H395">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I395">
-        <v>21992</v>
+        <v>0</v>
       </c>
       <c r="J395" t="str">
-        <v/>
+        <v>Build a long-form investigative reporting collection app for desktop browsers where every piece is grouped by the story series it belongs to, with a short summary at the top so I know what I'm getting into before I click — I want to be able to filter by topic or year, save pieces to a reading list, and pick up where I left off if I close the tab.</v>
       </c>
       <c r="K395" t="str">
-        <v/>
+        <v>做一个深度调查报道合集网页应用，在桌面浏览器上每篇作品按所属系列分组、顶部有简短摘要这样点击前知道是什么——能按话题或年份筛选、能保存到阅读清单、关闭标签页后能从离开的地方继续。</v>
       </c>
       <c r="L395" t="str">
-        <v>[q_web_057_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="396">
@@ -15448,19 +15448,19 @@
         <v>medium</v>
       </c>
       <c r="H396">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I396">
-        <v>21778</v>
+        <v>0</v>
       </c>
       <c r="J396" t="str">
-        <v/>
+        <v>Need a science explainer library app for the web where I can browse articles by topic, read through a clear explanation of a concept, and then take a short quiz at the end to see if it actually stuck — I want my quiz results saved so I can come back and track which topics I've actually learned versus just skimmed, all from a desktop browser.</v>
       </c>
       <c r="K396" t="str">
-        <v/>
+        <v>做一个科学讲解库网页应用，能按话题浏览文章、读清晰的概念解释、最后做简短小测验检验是否真的理解——测验成绩保存下来这样我能回来追踪哪些话题真的学会了相比只是浏览过，全在桌面浏览器上。</v>
       </c>
       <c r="L396" t="str">
-        <v>[q_web_057_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="397">
@@ -15486,19 +15486,19 @@
         <v>medium</v>
       </c>
       <c r="H397">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I397">
-        <v>18529</v>
+        <v>0</v>
       </c>
       <c r="J397" t="str">
-        <v/>
+        <v>Make a journalism learning app for desktop browsers where each lesson covers a specific reporting method — like how to verify sources or structure an investigation — with a short reading, a real-world example from an actual story, and a checklist of the steps involved so I can follow along practically, and a way to track which methods I've gone through.</v>
       </c>
       <c r="K397" t="str">
-        <v/>
+        <v>做一个记者学习应用给桌面浏览器，每堂课涵盖具体一个报道方法——比如如何核实信息或组织调查——包含简短阅读、真实故事中的实例、涉及的步骤清单这样我能实践跟进，还有办法追踪学过哪些方法。</v>
       </c>
       <c r="L397" t="str">
-        <v>[q_web_057_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="398">
@@ -15524,19 +15524,19 @@
         <v>medium</v>
       </c>
       <c r="H398">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="I398">
-        <v>17160</v>
+        <v>0</v>
       </c>
       <c r="J398" t="str">
-        <v/>
+        <v>Make a historical newspaper research app for desktop browsers where old newspaper pages are browsable by date and topic, each issue has notes explaining the context of major stories, and I can highlight or bookmark specific articles to come back to — I want a search that actually works across all the issues so I can find references to a specific event without clicking through page by page.</v>
       </c>
       <c r="K398" t="str">
-        <v/>
+        <v>做一个历史报纸研究应用给桌面浏览器，老报纸页面可按日期和话题浏览、每期有注释说明重要故事的时代背景、能高亮或收藏特定文章以后阅读——搜索功能跨所有期报纸工作这样我能找历史事件的参考而不用逐页点。</v>
       </c>
       <c r="L398" t="str">
-        <v>[q_web_057_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="399">
@@ -15562,19 +15562,19 @@
         <v>medium</v>
       </c>
       <c r="H399">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="I399">
-        <v>25221</v>
+        <v>0</v>
       </c>
       <c r="J399" t="str">
-        <v/>
+        <v>A data journalism learning hub app for the browser where tutorials are organized step by step — starting from how to find and clean data all the way to building a finished story — and each tutorial links to a real published project so you can see what it looks like done well, with a checklist on each tutorial so I can keep track of what I've finished, all running in a desktop browser.</v>
       </c>
       <c r="K399" t="str">
-        <v/>
+        <v>做一个数据新闻学学习中心网页应用给浏览器，教程按步骤组织——从怎么找和清理数据一路到做好完整故事——每个教程链到真实发表项目这样能看高手做成什么样、每个教程有清单这样我能追踪完成到哪里，全在桌面浏览器运行。</v>
       </c>
       <c r="L399" t="str">
-        <v>[q_web_057_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="400">
@@ -15600,19 +15600,19 @@
         <v>medium</v>
       </c>
       <c r="H400">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I400">
-        <v>19336</v>
+        <v>0</v>
       </c>
       <c r="J400" t="str">
-        <v/>
+        <v>Build a reader comments app for a media community site where people can leave their thoughts on articles, reply to each other, and vote on the most helpful comments, all running in a desktop browser so it feels natural to read and respond with a proper keyboard — I'd love the comment list to show the author's name and a little timestamp, and let logged-in readers sort by newest or most liked.</v>
       </c>
       <c r="K400" t="str">
-        <v/>
+        <v>为媒体社区网站构建一个读者评论应用，人们可以分享对文章的想法、互相回复、投票支持最有帮助的评论。应用在桌面浏览器上运行，用键盘阅读和回复很自然。评论列表要显示作者名字和时间戳，已登录的读者可以按最新或最受欢迎排序。</v>
       </c>
       <c r="L400" t="str">
-        <v>[q_web_058_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="401">
@@ -15638,19 +15638,19 @@
         <v>medium</v>
       </c>
       <c r="H401">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I401">
-        <v>19977</v>
+        <v>0</v>
       </c>
       <c r="J401" t="str">
-        <v/>
+        <v>Create a user content submission tool for a media community website where everyday readers can write and post their own articles or short stories, add a cover image, pick a topic category, and submit for review — it should feel approachable and fun to tinker with, running in a browser for desktop so people can type comfortably, with a simple preview of how the post will look before they send it in.</v>
       </c>
       <c r="K401" t="str">
-        <v/>
+        <v>为媒体社区网站创建用户内容投稿工具，让普通读者能写文章或短篇故事、添加封面图、选择话题分类、提交审核。应用要让人觉得有趣、容易上手，在桌面浏览器上运行，用户可以舒适地打字。提供简单的预览功能，让用户在提交前看到文章的最终效果。</v>
       </c>
       <c r="L401" t="str">
-        <v>[q_web_058_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="402">
@@ -15676,19 +15676,19 @@
         <v>medium</v>
       </c>
       <c r="H402">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="I402">
-        <v>20133</v>
+        <v>0</v>
       </c>
       <c r="J402" t="str">
-        <v/>
+        <v>Create a reader club app for a media community website where members can join reading groups around specific topics, see what others in the group are currently reading, and chat or leave short notes about a shared piece — it should work nicely in a desktop browser, and I'd love a sidebar that shows active club members and a feed of recent group activity so the place feels lively and worth coming back to.</v>
       </c>
       <c r="K402" t="str">
-        <v/>
+        <v>为媒体社区网站创建读者俱乐部应用，会员可以加入围绕特定话题的阅读小组、查看组内成员正在读什么、讨论或记笔记。应用在桌面浏览器上表现出色，有侧边栏显示活跃成员和最近的小组动态，让社区充满活力，值得经常回访。</v>
       </c>
       <c r="L402" t="str">
-        <v>[q_web_058_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="403">
@@ -15714,19 +15714,19 @@
         <v>medium</v>
       </c>
       <c r="H403">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I403">
-        <v>20205</v>
+        <v>0</v>
       </c>
       <c r="J403" t="str">
-        <v/>
+        <v>Build a collaborative fact-checking app for a media community website where readers can flag questionable claims in news articles, add sources or evidence supporting or challenging those claims, and upvote the most useful contributions — it should run in a desktop browser with a split layout where the original article text sits alongside the community notes, so readers can follow along and fact-check in one place.</v>
       </c>
       <c r="K403" t="str">
-        <v/>
+        <v>为媒体社区网站构建协作事实核查应用，读者可以标记新闻文章中的可疑说法、添加支持或反驳的资料、投票支持有用的贡献。应用在桌面浏览器运行，采用分栏布局，原文在一侧、社区笔记在另一侧，读者可以在一个地方同时跟进和核查内容。</v>
       </c>
       <c r="L403" t="str">
-        <v>[q_web_058_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="404">
@@ -15752,19 +15752,19 @@
         <v>medium</v>
       </c>
       <c r="H404">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I404">
-        <v>20395</v>
+        <v>0</v>
       </c>
       <c r="J404" t="str">
-        <v/>
+        <v>A tip board app for investigative journalists running in a browser for desktop, where the public can anonymously submit leads or source tips on ongoing stories, organized by topic so reporters can scan what's coming in quickly — the submission form should be simple enough that anyone can fill it out, and journalists should be able to mark tips as reviewed or worth following up.</v>
       </c>
       <c r="K404" t="str">
-        <v/>
+        <v>为调查记者构建一个线索板应用，在浏览器桌面版运行，公众可以匿名提交关于在进行的新闻选题的线索或来源信息，按话题分类方便记者快速浏览。投稿表单简洁易填，记者可以标记线索为已审阅或值得跟进。</v>
       </c>
       <c r="L404" t="str">
-        <v>[q_web_058_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="405">
@@ -15790,19 +15790,19 @@
         <v>medium</v>
       </c>
       <c r="H405">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I405">
-        <v>23187</v>
+        <v>0</v>
       </c>
       <c r="J405" t="str">
-        <v/>
+        <v>Make a monthly reading challenge tracker for magazine subscribers, running as a web app for desktop browsers, where subscribers can see how many articles they've read that month, where they land on a community leaderboard compared to other subscribers, and what reading milestone badges they've earned — I want the home screen of the app to show the current challenge goal and a scrollable list of the top readers with their counts.</v>
       </c>
       <c r="K405" t="str">
-        <v/>
+        <v>为杂志订阅用户制作每月阅读挑战追踪应用，在桌面浏览器上作为网络应用运行。订阅用户可以看到本月读过多少篇文章、在社区排行榜上的位置、赚取的阅读成就徽章。应用主屏显示当前挑战目标和可滚动的热读者排行榜及其阅读数。</v>
       </c>
       <c r="L405" t="str">
-        <v>[q_web_058_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="406">
@@ -15828,19 +15828,19 @@
         <v>medium</v>
       </c>
       <c r="H406">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I406">
-        <v>18566</v>
+        <v>0</v>
       </c>
       <c r="J406" t="str">
-        <v/>
+        <v>Make a RSS feed reader app for desktop browsers where I can paste in a bunch of feed links from different blogs and news sites and have them all show up in one place, so I stop wasting time hopping between tabs — I want the articles sorted by newest first, and a way to mark things as read so the unread stuff stays easy to spot.</v>
       </c>
       <c r="K406" t="str">
-        <v/>
+        <v>为桌面浏览器制作RSS订阅阅读器应用，用户可以粘贴不同博客和新闻网站的订阅链接，所有内容在一个地方显示，不用来回切换标签页。文章按最新优先排序，可以标记为已读，未读内容容易识别。</v>
       </c>
       <c r="L406" t="str">
-        <v>[q_web_059_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="407">
@@ -15866,19 +15866,19 @@
         <v>medium</v>
       </c>
       <c r="H407">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="I407">
-        <v>18613</v>
+        <v>0</v>
       </c>
       <c r="J407" t="str">
-        <v/>
+        <v>Make a news search tool that runs in a web app for desktop browsers where I can type in a keyword or topic and immediately get a list of relevant news articles pulled from different sources, with the headline, source name, and date all visible at a glance — I'm tired of going to five different sites to cross-check a story, so having filters for time range would really cut down the hassle.</v>
       </c>
       <c r="K407" t="str">
-        <v/>
+        <v>制作一个新闻搜索工具，在桌面浏览器的网络应用中运行。用户输入关键词或话题，立即从不同来源获取相关新闻文章，显示标题、来源名称和日期。支持时间范围过滤，避免用户在五个不同网站之间交叉验证。</v>
       </c>
       <c r="L407" t="str">
-        <v>[q_web_059_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="408">
@@ -15904,19 +15904,19 @@
         <v>medium</v>
       </c>
       <c r="H408">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I408">
-        <v>22590</v>
+        <v>0</v>
       </c>
       <c r="J408" t="str">
-        <v/>
+        <v>Need a newsroom calendar planner app that runs in a browser for desktop, where the team can schedule stories and assignments on a monthly calendar view, add notes about who's writing what and when it's due, so nobody has to chase people down asking what's in progress — it should be easy to click a day and add a new story slot with a title, assigned writer, and deadline.</v>
       </c>
       <c r="K408" t="str">
-        <v/>
+        <v>需要一个新闻编辑室日历规划应用，在桌面浏览器运行。团队可以在月历视图上安排故事和任务，添加谁负责写什么、什么时候截稿的笔记，省去追问进展的麻烦。用户点击某一天就能轻松添加故事槽位，输入标题、负责人和截稿时间。</v>
       </c>
       <c r="L408" t="str">
-        <v>[q_web_059_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="409">
@@ -15942,19 +15942,19 @@
         <v>medium</v>
       </c>
       <c r="H409">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="I409">
-        <v>18258</v>
+        <v>0</v>
       </c>
       <c r="J409" t="str">
-        <v/>
+        <v>Need a headline testing tracker that works as a web app for desktop browsers, where I can enter two different headline options for the same article, track how each one performs over time with click counts, and see a simple side-by-side comparison so I can tell which headline is actually working better — I'm tired of just guessing which title to use and this would save me a lot of second-guessing.</v>
       </c>
       <c r="K409" t="str">
-        <v/>
+        <v>需要一个标题效果测试追踪器，作为桌面浏览器网络应用。用户可以为同一篇文章输入两个不同的标题选项，追踪一段时间内的点击数表现，进行简单的并排对比，看哪个标题效果更好。省去猜测和反复确认标题选择的麻烦。</v>
       </c>
       <c r="L409" t="str">
-        <v>[q_web_059_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="410">
@@ -15980,19 +15980,19 @@
         <v>medium</v>
       </c>
       <c r="H410">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I410">
-        <v>19545</v>
+        <v>0</v>
       </c>
       <c r="J410" t="str">
-        <v/>
+        <v>A press release writing and sending tool for desktop browsers where I can draft a release using a clean text editor, fill in the basic details like title, date, and contact info, and then distribute it to a saved list of media contacts in one go — the app should let me manage my contacts list and keep a record of past releases I've sent so I can find them again later.</v>
       </c>
       <c r="K410" t="str">
-        <v/>
+        <v>为桌面浏览器制作新闻稿撰写和发布工具。用户可以用简洁的文本编辑器起草新闻稿、填入标题、日期和联系信息等基本细节，然后一次性分发给已保存的媒体联系人列表。应用可以管理联系人列表、保存发布历史，方便用户日后查找。</v>
       </c>
       <c r="L410" t="str">
-        <v>[q_web_059_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="411">
@@ -16018,19 +16018,19 @@
         <v>medium</v>
       </c>
       <c r="H411">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I411">
-        <v>22207</v>
+        <v>0</v>
       </c>
       <c r="J411" t="str">
-        <v/>
+        <v>Build a journalist contacts manager that runs as a web app for desktop browsers, where I can store all my sources and expert contacts in one place, add notes about each person like what topics they cover or the last time we spoke, and quickly search by name or subject when I need to reach someone for a story — it should also let me log past conversations so I never forget what a source told me.</v>
       </c>
       <c r="K411" t="str">
-        <v/>
+        <v>构建一个记者联系人管理器，作为桌面浏览器网络应用。用户可以在一个地方存储所有消息来源和专家联系人、添加关于每个人的笔记（如他们关注的话题、上次谈话时间），需要采访时快速按名字或话题搜索。还可以记录过往谈话，避免遗忘消息来源的信息。</v>
       </c>
       <c r="L411" t="str">
-        <v>[q_web_059_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="412">
@@ -16056,19 +16056,19 @@
         <v>medium</v>
       </c>
       <c r="H412">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I412">
-        <v>21370</v>
+        <v>0</v>
       </c>
       <c r="J412" t="str">
-        <v/>
+        <v>Create a museum website app for desktop browsers that has the kind of quiet, editorial feel you get from a well-designed art catalog — muted tones, generous whitespace, big beautiful images for each collection — where visitors can browse current and upcoming exhibitions, read about the museum's permanent collections, and find practical info like hours and ticketing all in one polished place.</v>
       </c>
       <c r="K412" t="str">
-        <v/>
+        <v>为桌面浏览器创建博物馆网站应用，具有精美艺术目录的那种安静、社论感——柔和色调、充足的留白、每个展品的精美大图。访客可以浏览当前和即将举办的展览、阅读博物馆永久馆藏的介绍、在一个精心设计的页面上找到营业时间和售票等实用信息。</v>
       </c>
       <c r="L412" t="str">
-        <v>[q_web_060_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="413">
@@ -16094,19 +16094,19 @@
         <v>medium</v>
       </c>
       <c r="H413">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I413">
-        <v>21268</v>
+        <v>0</v>
       </c>
       <c r="J413" t="str">
-        <v/>
+        <v>Create a website for an art festival or exhibition that feels like flipping through a beautifully curated printed program — rich visuals, thoughtful typography, with a warm and considered mood rather than something cold and corporate — running on desktop browsers, where visitors can explore all the participating artists, browse events by date, and get a real sense of the festival's identity just from how the thing looks and feels.</v>
       </c>
       <c r="K413" t="str">
-        <v/>
+        <v>为艺术节或展览创建网站，如同翻阅精心策划的印刷项目单——丰富的视觉、讲究的排版、温暖体贴的气质而非冷冰冰的企业感。在桌面浏览器运行，访客可以探索参展艺术家、按日期浏览活动、从网站的外观和感受真实体会艺术节的特色。</v>
       </c>
       <c r="L413" t="str">
-        <v>[q_web_060_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="414">
@@ -16132,19 +16132,19 @@
         <v>medium</v>
       </c>
       <c r="H414">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I414">
-        <v>20632</v>
+        <v>0</v>
       </c>
       <c r="J414" t="str">
-        <v/>
+        <v>An architecture and heritage site showcase website for desktop browsers that feels like a coffee table book brought to life online — full-bleed photography, unhurried pacing, elegant typography — where each landmark gets its own dedicated space with historical context, a photo gallery, and location details, so visitors can genuinely appreciate the beauty and story behind each place.</v>
       </c>
       <c r="K414" t="str">
-        <v/>
+        <v>为桌面浏览器制作建筑和文化遗产展示网站，如同精装咖啡桌图书在线呈现——满幅摄影、不急不躁的节奏、优雅的排版。每个地标有专属展示空间，包含历史背景、图片库和位置详情，让访客真正欣赏每个地方的美和故事。</v>
       </c>
       <c r="L414" t="str">
-        <v>[q_web_060_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="415">
@@ -16170,19 +16170,19 @@
         <v>medium</v>
       </c>
       <c r="H415">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I415">
-        <v>18704</v>
+        <v>0</v>
       </c>
       <c r="J415" t="str">
-        <v/>
+        <v>A website for a religious or sacred site that carries a sense of calm and reverence — soft palettes, gentle transitions, nothing rushed or loud — running on desktop browsers, where visitors can read about the history and spiritual significance of the place, see a gallery of photographs that capture the atmosphere, and find visitor information presented in a way that feels respectful and welcoming.</v>
       </c>
       <c r="K415" t="str">
-        <v/>
+        <v>为宗教或圣地创建网站，传达宁静和肃穆之感——柔和的配色、温和的过渡、没有仓促或嘈杂的元素。在桌面浏览器运行，访客可以阅读该地的历史和精神意义、观看捕捉氛围的摄影库、找到以尊重和欢迎态度呈现的访客信息。</v>
       </c>
       <c r="L415" t="str">
-        <v>[q_web_060_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="416">
@@ -16208,19 +16208,19 @@
         <v>medium</v>
       </c>
       <c r="H416">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I416">
-        <v>18296</v>
+        <v>0</v>
       </c>
       <c r="J416" t="str">
-        <v/>
+        <v>Create a public library digital collections showcase website that feels warm and inviting, like walking into a well-loved library, with a slightly nostalgic typographic mood and careful color choices — running on desktop browsers — where residents can browse digitized books, photographs, and local history materials organized by theme, with a search bar on the home screen of the site so people can find something specific without having to click through everything.</v>
       </c>
       <c r="K416" t="str">
-        <v/>
+        <v>创建一个公共图书馆数字馆藏展示网站，温暖迎人，如同走进一个备受关爱的图书馆，带有略带怀旧的排版气质和精心的色彩选择。在桌面浏览器运行，用户可以按主题浏览已数字化的图书、照片和本地历史资料，主屏有搜索栏，用户可以快速查找无需逐页浏览。</v>
       </c>
       <c r="L416" t="str">
-        <v>[q_web_060_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="417">
@@ -16246,19 +16246,19 @@
         <v>medium</v>
       </c>
       <c r="H417">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I417">
-        <v>19190</v>
+        <v>0</v>
       </c>
       <c r="J417" t="str">
-        <v/>
+        <v>Build a national archive digital exhibit website that feels authoritative but still visually rich and interesting — think aged paper textures, sepia-tinged photography, and typography that has some historical personality — for desktop browsers, where visitors can browse exhibits organized by era or theme, zoom into high-resolution scans of historical documents, and read the stories behind the artifacts in a way that actually draws you in.</v>
       </c>
       <c r="K417" t="str">
-        <v/>
+        <v>构建国家档案馆数字展览网站，既权威又视觉丰富——陈旧纸张纹理、棕褐色摄影、有历史特色的排版。在桌面浏览器运行，访客可以按年代或主题浏览展览、缩放历史文献扫描件的高分辨率版本、阅读文物背后的故事，以吸引人的方式呈现。</v>
       </c>
       <c r="L417" t="str">
-        <v>[q_web_060_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="418">
@@ -16284,19 +16284,19 @@
         <v>medium</v>
       </c>
       <c r="H418">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I418">
-        <v>19083</v>
+        <v>0</v>
       </c>
       <c r="J418" t="str">
-        <v/>
+        <v>An archive explorer app for desktop browsers that feels like wandering through a dimly lit special collections room — aged and atmospheric, with that mix of gravitas and quiet wonder — where you can browse historical documents and records organized along a timeline, click into an entry to read the full text alongside any scanned images, and the whole thing has that slow, considered pacing that makes old materials feel precious rather than just filed away.</v>
       </c>
       <c r="K418" t="str">
-        <v/>
+        <v>为桌面浏览器制作档案浏览应用，如同在昏暗的特藏室里漫步——年代久远、氛围深沉、既有庄严又有静谧的奇妙感。用户可以按时间线浏览历史文献和记录、点击条目阅读全文及任何扫描图像、整个应用节奏缓慢周全，让古老资料显得珍贵而非仅仅归档。</v>
       </c>
       <c r="L418" t="str">
-        <v>[q_web_061_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="419">
@@ -16322,19 +16322,19 @@
         <v>medium</v>
       </c>
       <c r="H419">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="I419">
-        <v>22752</v>
+        <v>0</v>
       </c>
       <c r="J419" t="str">
-        <v/>
+        <v>Create a research publishing site that feels like the kind of academic journal you'd actually want to read — clean, serious, with strong typographic hierarchy and a sense of intellectual care — running for desktop browsers, where researchers can share new findings organized by field or date, each entry with an abstract up front and the full piece below, and visitors can browse recent publications in a way that makes the work feel important and worth their time.</v>
       </c>
       <c r="K419" t="str">
-        <v/>
+        <v>创建学术研究发布网站，如同你真正想读的学术期刊——简洁、严肃、强烈的排版层级感和知识关怀。在桌面浏览器运行，研究人员可以分享按领域或日期组织的新发现，每条目前有摘要、下面是全文，访客可以以使研究显得重要、值得花时间的方式浏览最新发布。</v>
       </c>
       <c r="L419" t="str">
-        <v>[q_web_061_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="420">
@@ -16360,19 +16360,19 @@
         <v>medium</v>
       </c>
       <c r="H420">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="I420">
-        <v>21304</v>
+        <v>0</v>
       </c>
       <c r="J420" t="str">
-        <v/>
+        <v>A manifesto and advocacy declaration site for desktop browsers where the whole thing feels like a statement — bold, intentional, and a little bit urgent, the kind of design that makes you feel something before you've even read a word — where the text of the declaration is front and center, beautifully typeset, with space for signatories to be listed and a way for visitors to add their name to show their support.</v>
       </c>
       <c r="K420" t="str">
-        <v/>
+        <v>为桌面浏览器制作宣言和倡议宣言网站，整个页面如同一份声明——大胆、意图明确、略显紧迫，这种设计让人未读一字就有所感受。宣言文本居中突出、精美排版、留出签署人名单并允许访客添加名字表示支持。</v>
       </c>
       <c r="L420" t="str">
-        <v>[q_web_061_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="421">
@@ -16398,19 +16398,19 @@
         <v>medium</v>
       </c>
       <c r="H421">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I421">
-        <v>18436</v>
+        <v>0</v>
       </c>
       <c r="J421" t="str">
-        <v/>
+        <v>Need a public announcements site that carries a sense of clarity and trustworthiness — clean layout, readable typefaces, nothing fussy — for desktop browsers, where an organization can post official notices organized by date and category, and visitors can scan recent announcements easily and click through to read the full text, with older posts still accessible so nothing important gets lost.</v>
       </c>
       <c r="K421" t="str">
-        <v/>
+        <v>需要一个公告网站，传达清晰和可信感——简洁布局、易读字体、不繁琐。在桌面浏览器运行，组织可以发布按日期和类别组织的官方公告，访客可以轻松浏览最新公告并点击阅读全文，旧公告仍可访问，重要信息不会丢失。</v>
       </c>
       <c r="L421" t="str">
-        <v>[q_web_061_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="422">
@@ -16436,19 +16436,19 @@
         <v>medium</v>
       </c>
       <c r="H422">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I422">
-        <v>20838</v>
+        <v>0</v>
       </c>
       <c r="J422" t="str">
-        <v/>
+        <v>Create a city open data publishing site that feels approachable and well-organized rather than intimidating — soft, civic-minded colors, clear labels, a tone that says "this is for you" — for desktop browsers, where residents can browse datasets published by the city organized by topic like transport, environment, or finance, read plain-language descriptions of what each dataset contains, and download files directly from the site.</v>
       </c>
       <c r="K422" t="str">
-        <v/>
+        <v>创建城市开放数据发布网站，显得平易近人、组织有序而非令人畏惧——柔和的市民色调、清晰的标签、传达"这是给你的"的语气。在桌面浏览器运行，居民可以浏览城市发布的数据集，按交通、环境、财政等主题组织，阅读纯文本的数据集介绍、直接从网站下载文件。</v>
       </c>
       <c r="L422" t="str">
-        <v>[q_web_061_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="423">
@@ -16474,19 +16474,19 @@
         <v>medium</v>
       </c>
       <c r="H423">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I423">
-        <v>18585</v>
+        <v>0</v>
       </c>
       <c r="J423" t="str">
-        <v/>
+        <v>A digital oral history site for desktop browsers with a warm, intimate feel — think handwritten notes, family photo album vibes, soft warm tones — where community members can listen to recorded personal stories, read transcripts alongside the audio, and browse by narrator or theme so it feels like you're getting to know real people rather than just consuming content.</v>
       </c>
       <c r="K423" t="str">
-        <v/>
+        <v>为桌面浏览器制作数字口头历史网站，温暖、亲密的感受——手写笔记、家庭相册的气质、温和的暖色调。社区成员可以听录制的个人故事、边听边读文字记录、按讲述者或主题浏览，让人觉得在认识真实的人而非仅消费内容。</v>
       </c>
       <c r="L423" t="str">
-        <v>[q_web_061_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="424">
@@ -16512,19 +16512,19 @@
         <v>medium</v>
       </c>
       <c r="H424">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I424">
-        <v>19648</v>
+        <v>0</v>
       </c>
       <c r="J424" t="str">
-        <v/>
+        <v>Build a fundraising campaign site that has real soul to it — the kind of website that feels like it was made by people who genuinely care about the cause, with a warm personality and a look that earns trust rather than just asking for money — for desktop browsers, where visitors can read the story behind the campaign, see a live progress tracker showing how close the goal is, and contribute directly on the same page.</v>
       </c>
       <c r="K424" t="str">
-        <v/>
+        <v>构建一个有真挚灵魂的筹款活动网站——那种由真心关心事业的人制作的网站、温暖的个性、赢得信任而非单纯要钱的外观。在桌面浏览器运行，访客可以读活动故事、看实时进度追踪器显示目标有多接近、直接在页面上贡献。</v>
       </c>
       <c r="L424" t="str">
-        <v>[q_web_062_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="425">
@@ -16550,19 +16550,19 @@
         <v>medium</v>
       </c>
       <c r="H425">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I425">
-        <v>20864</v>
+        <v>0</v>
       </c>
       <c r="J425" t="str">
-        <v/>
+        <v>A campaign app with real soul — the kind of space that feels like it actually stands for something, not just another generic sign-up form — where people can read what the cause is about, add their name to show they're behind it, and see a live count of supporters growing in real time, all in a web app built for desktop browsers with a clean two-column layout that puts the campaign statement front and center alongside the supporter list.</v>
       </c>
       <c r="K425" t="str">
-        <v/>
+        <v>一个有真挚灵魂的活动应用——那种真正立场鲜明而非泛泛之辈的空间，让人们读懂事业内核、添加名字表示支持、实时看支持者数量增长。网络应用在桌面浏览器运行，干净的双列布局，活动声明和支持者列表并列突出。</v>
       </c>
       <c r="L425" t="str">
-        <v>[q_web_062_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="426">
@@ -16588,19 +16588,19 @@
         <v>medium</v>
       </c>
       <c r="H426">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="I426">
-        <v>22677</v>
+        <v>0</v>
       </c>
       <c r="J426" t="str">
-        <v/>
+        <v>Need a volunteer recruitment app that carries a certain warmth and sincerity — something that feels like it actually values the people showing up, not just filling slots — where prospective volunteers can browse open roles with a short description of what each one means and why it matters, fill out a simple sign-up form, and get a confirmation that feels human and personal, all working smoothly in a browser-based tool for desktop.</v>
       </c>
       <c r="K426" t="str">
-        <v/>
+        <v>需要一个志愿者招募应用，传达某种温暖和真诚——让人觉得真正被重视而非仅仅填补空位的感觉。志愿者可以浏览开放岗位、看到每个岗位的简短说明及其意义、填写简单的报名表、得到有人情味的个性化确认。应用在桌面的网络工具中顺畅运行。</v>
       </c>
       <c r="L426" t="str">
-        <v>[q_web_062_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="427">
@@ -16626,19 +16626,19 @@
         <v>medium</v>
       </c>
       <c r="H427">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="I427">
-        <v>20732</v>
+        <v>0</v>
       </c>
       <c r="J427" t="str">
-        <v/>
+        <v>A fundraising campaign app with a personality and a point of view — the kind that makes a donor feel like their contribution is part of something meaningful, not just a transaction — where the main area shows the cause story with real weight, a progress bar that actually feels alive, and a simple way to give, all living inside a web app designed for desktop with a sidebar that keeps the campaign's identity and total raised always visible.</v>
       </c>
       <c r="K427" t="str">
-        <v/>
+        <v>一个有个性和态度的筹款活动应用——让捐赠者觉得自己的贡献是有意义的事业的一部分、而非仅交易。主区域展现事业故事、有生气的进度条、简单的捐赠方式，作为为桌面设计的网络应用、侧边栏始终显示活动身份和筹集总额。</v>
       </c>
       <c r="L427" t="str">
-        <v>[q_web_062_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="428">
@@ -16664,19 +16664,19 @@
         <v>medium</v>
       </c>
       <c r="H428">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I428">
-        <v>23666</v>
+        <v>0</v>
       </c>
       <c r="J428" t="str">
-        <v/>
+        <v>A museum membership annual drive app that feels like the museum itself — cultivated taste, a quiet confidence — where the home screen leads with a compelling reason to become a member this year, followed by a clean breakdown of the membership tiers and their perks, and a straightforward way to sign up, all running as a web app for desktop browsers with enough visual breathing room that the whole thing feels considered rather than rushed.</v>
       </c>
       <c r="K428" t="str">
-        <v/>
+        <v>一个博物馆会员年度筹款应用，感觉如同博物馆本身——品味精湛、静然自信。主屏突出今年成为会员的compelling理由，然后清晰列出会员等级及福利、直接的注册方式。作为桌面浏览器网络应用运行，有充足的视觉呼吸空间，整体显得深思熟虑而非仓促。</v>
       </c>
       <c r="L428" t="str">
-        <v>[q_web_062_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="429">
@@ -16702,19 +16702,19 @@
         <v>medium</v>
       </c>
       <c r="H429">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="I429">
-        <v>20164</v>
+        <v>0</v>
       </c>
       <c r="J429" t="str">
-        <v/>
+        <v>Create a symphony orchestra season ticket promotional app that has the right atmosphere — elegant but inviting, not cold — where visitors can browse the upcoming season's program highlights, see the different seating packages with honest pricing, and move through a clean checkout flow, all as a website built for desktop with a layout that puts the music and the story of the season at the forefront rather than burying it under forms.</v>
       </c>
       <c r="K429" t="str">
-        <v/>
+        <v>创建交响乐团季票促销应用，有恰当的气氛——优雅却欢迎、不冷漠。访客可以浏览即将到来的演季亮点、看不同座位套餐及诚实的定价、经历简洁的结账流程。作为为桌面设计的网站、布局突出音乐和演季故事而非表格繁琐。</v>
       </c>
       <c r="L429" t="str">
-        <v>[q_web_062_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="430">
@@ -16740,19 +16740,19 @@
         <v>medium</v>
       </c>
       <c r="H430">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I430">
-        <v>19382</v>
+        <v>0</v>
       </c>
       <c r="J430" t="str">
-        <v/>
+        <v>Make a souvenir shop app for a cultural venue where I can actually keep track of all the items we sell without things getting messy, running as a web app on desktop browsers, with a simple product listing on the left and a quick way to add or update items on the right, plus a basic cart and checkout flow so visitors can browse and buy something without me having to manage it manually every time.</v>
       </c>
       <c r="K430" t="str">
-        <v/>
+        <v>为文化场所制作纪念品商店应用，我可以实时追踪所有销售商品而不用担心混乱——在桌面浏览器作为网络应用运行。左侧简单的产品列表、右侧快速添加或更新商品、基本的购物车和结账流程，访客可以浏览和购买而不用我每次都手动管理。</v>
       </c>
       <c r="L430" t="str">
-        <v>[q_web_063_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="431">
@@ -16778,19 +16778,19 @@
         <v>medium</v>
       </c>
       <c r="H431">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I431">
-        <v>19584</v>
+        <v>0</v>
       </c>
       <c r="J431" t="str">
-        <v/>
+        <v>Need a ticket sales app for a venue or event that just handles the whole thing end to end without me having to chase people for payment or keep track in a spreadsheet — a browser-based tool for desktop where customers can pick a date, choose how many tickets they want, pay, and get a confirmation, and I can see all the orders in one place without anything falling through the cracks.</v>
       </c>
       <c r="K431" t="str">
-        <v/>
+        <v>需要一个票务销售应用，整个流程端到端处理而不用我追要款或用电子表格追踪——桌面浏览器的网络工具。顾客可以选日期、选票数、支付、得到确认，我可以在一个地方看到所有订单而不用漏掉任何信息。</v>
       </c>
       <c r="L431" t="str">
-        <v>[q_web_063_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="432">
@@ -16816,19 +16816,19 @@
         <v>medium</v>
       </c>
       <c r="H432">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I432">
-        <v>21978</v>
+        <v>0</v>
       </c>
       <c r="J432" t="str">
-        <v/>
+        <v>Need a donation app that makes it easy for people to actually complete a contribution without getting confused or dropping off halfway — a web app for desktop where donors can pick an amount or type in their own, fill out just the essentials, and get a clear confirmation that their donation went through, with a simple summary on the side showing what the funds are going toward so people feel good about clicking that button.</v>
       </c>
       <c r="K432" t="str">
-        <v/>
+        <v>需要一个捐赠应用，让人们容易完成贡献而不迷茫或中途放弃——桌面浏览器的网络应用。捐赠者可以选金额或自定义、填最少的必填项、清楚地确认捐赠已通过，侧边有简单的总结显示资金用途，让人有好感地点击捐赠按钮。</v>
       </c>
       <c r="L432" t="str">
-        <v>[q_web_063_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="433">
@@ -16854,19 +16854,19 @@
         <v>medium</v>
       </c>
       <c r="H433">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="I433">
-        <v>20254</v>
+        <v>0</v>
       </c>
       <c r="J433" t="str">
-        <v/>
+        <v>Create a membership renewal app that takes the hassle out of chasing people down every year — a web app for desktop browsers where members can log in, see their current membership status and expiration date, pick a renewal period, and pay in a few clicks without having to re-enter all their info from scratch, and I get a clear view of who has renewed and who still needs a nudge.</v>
       </c>
       <c r="K433" t="str">
-        <v/>
+        <v>创建会员续费应用，省去每年追着人缴费的麻烦——桌面浏览器网络应用。会员可以登录、看当前会员状态和过期日期、选续费期限、几个点击完成支付而不用重新填信息。我可以清楚地看到谁已续费、谁还需提醒。</v>
       </c>
       <c r="L433" t="str">
-        <v>[q_web_063_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="434">
@@ -16892,19 +16892,19 @@
         <v>medium</v>
       </c>
       <c r="H434">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I434">
-        <v>20440</v>
+        <v>0</v>
       </c>
       <c r="J434" t="str">
-        <v/>
+        <v>Build a museum art print and reproduction licensing store app as a web app for desktop where people can browse available artworks by category, see the different license types and what each one covers, pick the size or format they need, and complete the purchase without having to email someone back and forth to figure out the details — just a clean self-serve flow that handles the whole transaction.</v>
       </c>
       <c r="K434" t="str">
-        <v/>
+        <v>构建博物馆艺术印刷品和复制授权商店应用，作为桌面网络应用。用户可以按类别浏览可用艺术作品、看不同授权类型及其涵盖内容、选需要的尺寸或格式、完成购买而不用来回邮件商议细节。简洁的自助流程处理整个交易。</v>
       </c>
       <c r="L434" t="str">
-        <v>[q_web_063_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="435">
@@ -16930,19 +16930,19 @@
         <v>medium</v>
       </c>
       <c r="H435">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I435">
-        <v>20771</v>
+        <v>0</v>
       </c>
       <c r="J435" t="str">
-        <v/>
+        <v>Need a guided tour booking and payment app for a heritage site that removes all the back-and-forth of coordinating visits manually — a browser-based tool for desktop where visitors can see available tour slots, pick a time, choose how many people, pay right there, and get a booking confirmation, while the site admin can see the schedule fill up and manage capacity without managing a separate inbox.</v>
       </c>
       <c r="K435" t="str">
-        <v/>
+        <v>需要一个导览预约和支付应用，消除手动协调访问的来回沟通——桌面浏览器网络工具。访客可以看可用导览时段、选时间、选人数、当场支付、得到预约确认。网站管理员可以看日程怎样排满、管理容量而不用单独管理收件箱。</v>
       </c>
       <c r="L435" t="str">
-        <v>[q_web_063_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="436">
@@ -16968,19 +16968,19 @@
         <v>medium</v>
       </c>
       <c r="H436">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I436">
-        <v>18639</v>
+        <v>0</v>
       </c>
       <c r="J436" t="str">
-        <v/>
+        <v>Make a visit booking app for a cultural institution that takes away the headache of managing reservations by hand — a web app for desktop browsers where visitors can pick a date from a calendar, choose a time slot, fill in how many people are coming, and submit their booking in one go, with a confirmation they can reference later, and a simple way for staff to see who is coming and when without digging through emails.</v>
       </c>
       <c r="K436" t="str">
-        <v/>
+        <v>为文化机构制作访问预约应用，省去手动管理预订的麻烦——桌面浏览器网络应用。访客可以从日历选日期、选时间段、填人数、一次性提交预约，得到可供日后参考的确认。工作人员可以简单地看到谁什么时候来而不用挖邮件。</v>
       </c>
       <c r="L436" t="str">
-        <v>[q_web_064_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="437">
@@ -17006,19 +17006,19 @@
         <v>medium</v>
       </c>
       <c r="H437">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I437">
-        <v>18265</v>
+        <v>0</v>
       </c>
       <c r="J437" t="str">
-        <v/>
+        <v>Create an event sign-up app that makes it dead simple for people to register for activities without me having to manage it all by hand — a web app built for desktop browsers where visitors can see what events are happening, click to register, fill out a short form with just their name and contact info, and get a confirmation instantly, while I can check who has signed up for each event in one tidy list.</v>
       </c>
       <c r="K437" t="str">
-        <v/>
+        <v>创建活动报名应用，让人们简单地注册活动而不用我手动管理——为桌面浏览器设计的网络应用。访客可以看什么活动进行、点击报名、填简短表单（仅名字和联系方式）、立即得到确认。我可以在一个整齐的列表中检查每个活动的报名人员。</v>
       </c>
       <c r="L437" t="str">
-        <v>[q_web_064_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="438">
@@ -17044,19 +17044,19 @@
         <v>medium</v>
       </c>
       <c r="H438">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I438">
-        <v>18030</v>
+        <v>0</v>
       </c>
       <c r="J438" t="str">
-        <v/>
+        <v>Build a guided tour reservation app that saves me from manually fielding requests every day — a web app for desktop where people can see which tour times are still open, pick the one that works for them, fill in their group size, and lock in the booking on their own, and I get a running list of all upcoming reservations so I can actually plan ahead instead of scrambling.</v>
       </c>
       <c r="K438" t="str">
-        <v/>
+        <v>构建导览预订应用，救我每天手动处理请求的麻烦——桌面网络应用。人们可以看哪些导览时间仍有空位、选适合他们的、填小组人数、自己锁定预约。我得到一份所有即将到来的预订列表，能够真正提前规划而非手忙脚乱。</v>
       </c>
       <c r="L438" t="str">
-        <v>[q_web_064_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="439">
@@ -17082,19 +17082,19 @@
         <v>medium</v>
       </c>
       <c r="H439">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="I439">
-        <v>20780</v>
+        <v>0</v>
       </c>
       <c r="J439" t="str">
-        <v/>
+        <v>Create a museum timed-entry ticket booking app that cuts out all the confusion of people showing up without a slot — a website for desktop browsers where visitors pick their visit date, choose an available time window, select ticket quantities, and check out cleanly, with a booking summary they can save or print, and a simple back-end view where staff can see how many people are coming in each time slot throughout the day.</v>
       </c>
       <c r="K439" t="str">
-        <v/>
+        <v>创建博物馆定时入场票预约应用，消除人们无时段就来的混乱——桌面浏览器网站。访客选访问日期、选可用时间窗、选票数、干净地结账，得到可保存或打印的预约总结。工作人员简单地看到全天各时间段有多少人要来。</v>
       </c>
       <c r="L439" t="str">
-        <v>[q_web_064_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="440">
@@ -17120,19 +17120,19 @@
         <v>medium</v>
       </c>
       <c r="H440">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="I440">
-        <v>21761</v>
+        <v>0</v>
       </c>
       <c r="J440" t="str">
-        <v/>
+        <v>Build a library study room reservation app that stops the constant "is this room free?" chaos — a web app for desktop browsers where students can see which rooms are available for a given day and time, pick the one they want, book it for a set number of hours, and get a confirmation they can actually show someone, with a simple view that shows all current bookings so staff can manage the schedule without a phone call every five minutes.</v>
       </c>
       <c r="K440" t="str">
-        <v/>
+        <v>构建图书馆自习室预约应用，停止无休止的"这间教室现在空吗"混乱——桌面浏览器网络应用。学生可以看某个日期时间有哪些教室可用、选想要的、按固定小时预约、得到可以展示的确认。工作人员简单地看到所有现有预约而不用每五分钟接一个电话。</v>
       </c>
       <c r="L440" t="str">
-        <v>[q_web_064_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="441">
@@ -17158,19 +17158,19 @@
         <v>medium</v>
       </c>
       <c r="H441">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="I441">
-        <v>19480</v>
+        <v>0</v>
       </c>
       <c r="J441" t="str">
-        <v/>
+        <v>Make a private viewing scheduler app for an art gallery where collectors or guests can request a curator-led session — a web app on desktop where the person fills in their preferred date and time, a short note about what they are interested in seeing, and submits the request, and the gallery side can review the incoming requests, confirm or suggest a different time, and keep track of all the scheduled viewings without losing anything in an email chain.</v>
       </c>
       <c r="K441" t="str">
-        <v/>
+        <v>为美术馆制作私人展览预约应用，收藏家或嘉宾可以申请策展人导览环节——桌面网络应用。申请者填首选日期时间、简短笔记说明感兴趣的内容、提交请求。美术馆方可以审核来单、确认或提议其他时间、追踪所有已排导览而无需在邮件链中遗漏信息。</v>
       </c>
       <c r="L441" t="str">
-        <v>[q_web_064_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="442">
@@ -17196,19 +17196,19 @@
         <v>medium</v>
       </c>
       <c r="H442">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="I442">
-        <v>19493</v>
+        <v>0</v>
       </c>
       <c r="J442" t="str">
-        <v/>
+        <v>Need a science education resource app that makes it easy to find and keep track of good learning materials in one place — a web app for desktop browsers where resources are organized by topic so I can jump straight to what I need, each entry has a title, a short description, and a link, and I can mark the ones I want to revisit so they do not get buried under everything else.</v>
       </c>
       <c r="K442" t="str">
-        <v/>
+        <v>需要一个科学教育资源应用，让人容易在一个地方找到和追踪好的学习资料——桌面浏览器网络应用。资源按话题组织，我可以直接跳到需要的内容、每条目有标题、简短描述和链接、可以标记想重温的以免埋没在其他内容里。</v>
       </c>
       <c r="L442" t="str">
-        <v>[q_web_065_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="443">
@@ -17234,19 +17234,19 @@
         <v>medium</v>
       </c>
       <c r="H443">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="I443">
-        <v>18716</v>
+        <v>0</v>
       </c>
       <c r="J443" t="str">
-        <v/>
+        <v>Create a digital archive app for storing and browsing historical documents and records in an organized way — a web app for desktop browsers where everything is sorted by category or date so I can find what I need fast, each record has a title, a brief description, and the actual file attached, and I can search by keyword so I am not scrolling through the whole collection every time I need something specific.</v>
       </c>
       <c r="K443" t="str">
-        <v/>
+        <v>创建数字档案应用，有组织地存储和浏览历史文献和记录——桌面浏览器网络应用。所有内容按类别或日期排序便于快速查找、每条记录有标题、简短描述和附加文件、可以按关键词搜索而不用每次都滚动整个馆藏。</v>
       </c>
       <c r="L443" t="str">
-        <v>[q_web_065_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="444">
@@ -17272,19 +17272,19 @@
         <v>medium</v>
       </c>
       <c r="H444">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="I444">
-        <v>21334</v>
+        <v>0</v>
       </c>
       <c r="J444" t="str">
-        <v/>
+        <v>Build an open course library app for a cultural or educational organization where all the available courses are listed clearly in one place — a web app for desktop browsers where each course has a title, a description of what it covers, and a way to enroll or access the materials, and I can filter by topic or level so I can find what fits what I am looking for without having to scroll through everything at once.</v>
       </c>
       <c r="K444" t="str">
-        <v/>
+        <v>为文化或教育机构构建开放课程库应用，所有可用课程在一个地方清晰列出——桌面浏览器网络应用。每课程有标题、涵盖内容描述、注册或获取资料的方式、可以按话题或级别过滤而不用一次滚动所有内容。</v>
       </c>
       <c r="L444" t="str">
-        <v>[q_web_065_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="445">
@@ -17310,19 +17310,19 @@
         <v>medium</v>
       </c>
       <c r="H445">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I445">
-        <v>21812</v>
+        <v>0</v>
       </c>
       <c r="J445" t="str">
-        <v/>
+        <v>A civic transparency learning app for local government that keeps everything organized and easy to actually find — where the home area shows the main topics people care about, like budget decisions, planning, or public meetings, each topic links to plain-language explainers and supporting documents, and there is a search bar so anyone can look up a specific issue without needing to know where to start, all running as a web app for desktop browsers.</v>
       </c>
       <c r="K445" t="str">
-        <v/>
+        <v>一个市政透明度学习应用，保持所有内容组织有序、容易真正查找——主区域显示人们关心的主要话题（如预算决议、规划、公众会议），每个话题链接到纯文本的解释器和支持文献，有搜索栏任何人都可以查找特定议题而不用知道从哪开始。作为桌面浏览器网络应用运行。</v>
       </c>
       <c r="L445" t="str">
-        <v>[q_web_065_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="446">
@@ -17348,19 +17348,19 @@
         <v>medium</v>
       </c>
       <c r="H446">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I446">
-        <v>21661</v>
+        <v>0</v>
       </c>
       <c r="J446" t="str">
-        <v/>
+        <v>A public library digital reading and skills hub app where everything is sorted and easy to navigate — the home screen lists reading collections and skill-building courses side by side so people can see both at once, each item has a clear title and a short note on what it covers, and there is a way to track what you have started or finished, all working as a web app for desktop browsers that the library can point patrons to.</v>
       </c>
       <c r="K446" t="str">
-        <v/>
+        <v>一个公共图书馆数字阅读和技能中心应用，所有内容排序有序、易于导航——主屏并列显示阅读馆藏和技能课程，人们一眼就能看到两者、每条目有清晰标题和简短说明、有追踪已开始或完成的内容的方式。作为桌面浏览器网络应用工作，图书馆可以推荐给用户。</v>
       </c>
       <c r="L446" t="str">
-        <v>[q_web_065_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="447">
@@ -17386,19 +17386,19 @@
         <v>medium</v>
       </c>
       <c r="H447">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I447">
-        <v>20406</v>
+        <v>0</v>
       </c>
       <c r="J447" t="str">
-        <v/>
+        <v>Build an endangered language learning app that is organized around the languages themselves so learners can find what they are looking for right away — a web app for desktop browsers where each language has its own space with basic lessons, audio clips to hear how words sound, and a vocabulary list you can work through at your own pace, with a simple way to pick up where you left off when you come back.</v>
       </c>
       <c r="K447" t="str">
-        <v/>
+        <v>构建濒危语言学习应用，围绕语言本身组织，学习者可以立即找到想要的内容——桌面浏览器网络应用。每种语言有自己的空间，包含基础课程、听单词发音的音频、可自定步调的词表、简单的方式能记得下次返回时的进度。</v>
       </c>
       <c r="L447" t="str">
-        <v>[q_web_065_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="448">
@@ -17424,19 +17424,19 @@
         <v>medium</v>
       </c>
       <c r="H448">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I448">
-        <v>19180</v>
+        <v>0</v>
       </c>
       <c r="J448" t="str">
-        <v/>
+        <v>Make a volunteer community app where people who care about local causes can find each other and coordinate — a web app that works well in a desktop browser, where volunteers can post what they are working on, browse what other people are doing, and sign up to help with something that interests them, with a simple profile for each person showing what they have been involved with so the community actually feels like a community and not just a list of names.</v>
       </c>
       <c r="K448" t="str">
-        <v/>
+        <v>制作志愿者社区应用，关心本地事业的人可以互相找到、协调——在桌面浏览器表现好的网络应用。志愿者可以发布自己正在做什么、浏览他人正在做什么、报名帮助感兴趣的事。每个人有简单的档案显示参与过的事，社区真的感觉像个社区而不仅是名字列表。</v>
       </c>
       <c r="L448" t="str">
-        <v>[q_web_066_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="449">
@@ -17462,19 +17462,19 @@
         <v>medium</v>
       </c>
       <c r="H449">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="I449">
-        <v>20726</v>
+        <v>0</v>
       </c>
       <c r="J449" t="str">
-        <v/>
+        <v>Build a community discussion app around cultural or civic topics where people can actually dig into an issue together — a web app that runs in a desktop browser, where anyone can post a question or topic they want to talk about, others can reply and build on each other's ideas, and everything is sorted so the most active conversations are easy to find, making it feel like a real back-and-forth rather than just comments disappearing into a void.</v>
       </c>
       <c r="K449" t="str">
-        <v/>
+        <v>构建围绕文化或市政话题的社区讨论应用，人们可以真正一起深入议题——在桌面浏览器运行的网络应用。任何人都可以发起想讨论的问题或话题、他人回复和建立想法、所有内容排序让最活跃的对话容易找到，显得真的互动而非评论消失无踪。</v>
       </c>
       <c r="L449" t="str">
-        <v>[q_web_066_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="450">
@@ -17500,19 +17500,19 @@
         <v>medium</v>
       </c>
       <c r="H450">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="I450">
-        <v>20842</v>
+        <v>0</v>
       </c>
       <c r="J450" t="str">
-        <v/>
+        <v>Need a web app for managing a believers and members circle, where people in the group can sign up as members, see a list of fellow members, and post little updates or messages to the group, and it should show who joined recently on the home screen so the community feels alive and active.</v>
       </c>
       <c r="K450" t="str">
-        <v/>
+        <v>需要一个网页应用，用来管理一个信教者和成员圈子，让小组里的人可以注册成为成员，查看其他成员的列表，然后发布一些小更新或消息给整个群组，首页应该显示最近加入的人，这样社区就感觉很活跃有生气。</v>
       </c>
       <c r="L450" t="str">
-        <v>[q_web_066_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="451">
@@ -17538,19 +17538,19 @@
         <v>medium</v>
       </c>
       <c r="H451">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I451">
-        <v>22425</v>
+        <v>0</v>
       </c>
       <c r="J451" t="str">
-        <v/>
+        <v>A neighborhood arts collective website where local artists can each post their work — paintings, photos, craft pieces, whatever — so the whole community can browse and leave comments, and it runs in the browser on desktop so you can really see the artwork nicely laid out side by side.</v>
       </c>
       <c r="K451" t="str">
-        <v/>
+        <v>一个本地艺术集体的网站，当地艺术家可以发布自己的作品——绘画、照片、手工艺品之类的——这样整个社区都能浏览和留言评论，而且是在桌面浏览器里运行，这样可以把艺术作品漂亮地并排展示出来。</v>
       </c>
       <c r="L451" t="str">
-        <v>[q_web_066_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="452">
@@ -17576,19 +17576,19 @@
         <v>medium</v>
       </c>
       <c r="H452">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="I452">
-        <v>18373</v>
+        <v>0</v>
       </c>
       <c r="J452" t="str">
-        <v/>
+        <v>Create a web app for a local heritage storytelling archive where community members can upload and share stories, old photos, and memories tied to places in the area, with a search bar so anyone visiting the site can find stories by location or topic and read them in a clean, organized way.</v>
       </c>
       <c r="K452" t="str">
-        <v/>
+        <v>做一个网页应用，用来建立本地文化遗产故事档案库，社区成员可以上传和分享故事、老照片、与本地地点相关的记忆，带有搜索框，这样访问者可以按位置或主题查找故事，然后用整洁规范的方式阅读。</v>
       </c>
       <c r="L452" t="str">
-        <v>[q_web_066_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="453">
@@ -17614,19 +17614,19 @@
         <v>medium</v>
       </c>
       <c r="H453">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I453">
-        <v>41187</v>
+        <v>0</v>
       </c>
       <c r="J453" t="str">
-        <v/>
+        <v>Make a web app for coordinating volunteers and vendors at a community festival, where organizers can post available time slots and task areas for volunteers to sign up for, and also keep a list of all the vendors with their booth info and what they're bringing, all in one place on the desktop browser so it's easy to manage everything leading up to the event.</v>
       </c>
       <c r="K453" t="str">
-        <v/>
+        <v>做一个网页应用，用来协调社区节庆的志愿者和摊主，组织者可以发布志愿者可以报名的时间段和任务区域，还可以保存所有摊主的清单，包括摊位信息和他们要带什么东西，全部在桌面浏览器的一个地方管理，这样活动前的准备工作就很轻松。</v>
       </c>
       <c r="L453" t="str">
-        <v>[q_web_066_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="454">
@@ -17652,19 +17652,19 @@
         <v>medium</v>
       </c>
       <c r="H454">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="I454">
-        <v>22992</v>
+        <v>0</v>
       </c>
       <c r="J454" t="str">
-        <v/>
+        <v>Make a web app that works like a public services portal, where people can go to find all the local government services in one spot — like applying for documents, paying fees, or booking appointments — so I don't have to hunt through a dozen different websites every time I need to deal with something official, and it should have a search bar right up front so I can just type what I need and get to the right place fast.</v>
       </c>
       <c r="K454" t="str">
-        <v/>
+        <v>做一个网页应用，就像一个公共服务门户，用户可以在一个地方找到所有本地政府服务——比如申请证件、缴费、预约——这样我就不用每次处理行政事务都要翻遍十几个网站，应该在最上面有个搜索框，这样我就可以直接输入需要什么，快速找到正确的地方。</v>
       </c>
       <c r="L454" t="str">
-        <v>[q_web_067_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="455">
@@ -17690,19 +17690,19 @@
         <v>medium</v>
       </c>
       <c r="H455">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="I455">
-        <v>23813</v>
+        <v>0</v>
       </c>
       <c r="J455" t="str">
-        <v/>
+        <v>Build a web app that works like a government services hall, where citizens can look up what paperwork they need for different types of requests, fill out and submit forms online, and then check the status of their applications without having to show up in person or call anyone, since the whole thing just wastes so much time otherwise.</v>
       </c>
       <c r="K455" t="str">
-        <v/>
+        <v>做一个网页应用，就像一个政务大厅，市民可以查询各种申请需要什么文件，在线填写和提交表格，然后查看申请状态，不需要亲自去办公厅或打电话，因为那样真的很浪费时间。</v>
       </c>
       <c r="L455" t="str">
-        <v>[q_web_067_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="456">
@@ -17728,19 +17728,19 @@
         <v>medium</v>
       </c>
       <c r="H456">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I456">
-        <v>21443</v>
+        <v>0</v>
       </c>
       <c r="J456" t="str">
-        <v/>
+        <v>Need a web app for hosting a virtual exhibition, where organizers can upload artwork or display items with descriptions, and visitors can browse through the whole exhibit in their desktop browser, clicking into individual pieces to read more, so people who can't attend a physical event can still enjoy and explore the whole show at their own pace.</v>
       </c>
       <c r="K456" t="str">
-        <v/>
+        <v>需要一个网页应用来举办虚拟展览，组织者可以上传艺术品或展品并附上说明，访问者可以在桌面浏览器里浏览整个展览，点击单件作品查看更多信息，这样无法参加线下活动的人也能按自己的节奏享受和探索整个展览。</v>
       </c>
       <c r="L456" t="str">
-        <v>[q_web_067_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="457">
@@ -17766,19 +17766,19 @@
         <v>medium</v>
       </c>
       <c r="H457">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="I457">
-        <v>24609</v>
+        <v>0</v>
       </c>
       <c r="J457" t="str">
-        <v/>
+        <v>A government permit tracker app for desktop browsers where you can fill out a permit application, submit it online, and then actually see where your request stands in the approval process, with a clear status list showing each step so you're not left wondering whether anyone has even looked at your paperwork.</v>
       </c>
       <c r="K457" t="str">
-        <v/>
+        <v>一个面向桌面浏览器的政务许可申报追踪应用，你可以填写许可申请，在线提交，然后实际看到你的申请在批准流程里的进展，有一个清晰的状态列表显示每一步，这样你就不会一直在那儿纠结是否有人看过你的申请材料。</v>
       </c>
       <c r="L457" t="str">
-        <v>[q_web_067_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="458">
@@ -17804,19 +17804,19 @@
         <v>medium</v>
       </c>
       <c r="H458">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I458">
-        <v>22761</v>
+        <v>0</v>
       </c>
       <c r="J458" t="str">
-        <v/>
+        <v>A nonprofit grant manager app that runs in the browser on desktop, where staff can keep track of all the grants they've applied for, log notes and deadlines for each one, and store the reports they need to send back to funders, so everything is in one place and nobody has to dig through email chains to figure out what's due next.</v>
       </c>
       <c r="K458" t="str">
-        <v/>
+        <v>一个非营利组织资金管理应用，在桌面浏览器里运行，员工可以跟踪所有申请过的资金，记录每笔资金的笔记和截止时间，还能存储需要发给资助者的报告，这样所有东西都在一个地方，没人需要挖电邮链才能搞清楚下一步该干什么。</v>
       </c>
       <c r="L458" t="str">
-        <v>[q_web_067_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="459">
@@ -17842,19 +17842,19 @@
         <v>medium</v>
       </c>
       <c r="H459">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I459">
-        <v>24325</v>
+        <v>0</v>
       </c>
       <c r="J459" t="str">
-        <v/>
+        <v>Build a web app for searching and browsing a digital archive of cultural heritage sites, where I can type in a name or region and pull up records with photos, historical notes, and related documents about each site, so it's actually possible to find things quickly rather than scrolling through endless unrelated results.</v>
       </c>
       <c r="K459" t="str">
-        <v/>
+        <v>做一个网页应用，用来搜索和浏览数字文化遗产档案库，我可以输入名字或地区，拉起相关记录，包含照片、历史笔记和每个地点的相关文件，这样真的能快速找到东西，而不是无尽地滚动查看不相关的结果。</v>
       </c>
       <c r="L459" t="str">
-        <v>[q_web_067_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="460">
@@ -17880,19 +17880,19 @@
         <v>medium</v>
       </c>
       <c r="H460">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I460">
-        <v>20111</v>
+        <v>0</v>
       </c>
       <c r="J460" t="str">
-        <v/>
+        <v>Need a web app that lets me put together a nice GitHub profile showcase site, where I can display my pinned projects with short descriptions and links, show a little bit about myself and what I'm working on these days, and have it all look clean when viewed on a desktop browser so people checking out my profile get a good impression.</v>
       </c>
       <c r="K460" t="str">
-        <v/>
+        <v>需要一个网页应用，让我能做一个漂亮的 GitHub 个人展示网站，可以展示我固定的项目和简短描述及链接，展示一点关于我自己和我最近在做什么，在桌面浏览器里看起来很整洁，这样检查我个人资料的人能留下好印象。</v>
       </c>
       <c r="L460" t="str">
-        <v>[q_web_068_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="461">
@@ -17918,19 +17918,19 @@
         <v>medium</v>
       </c>
       <c r="H461">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I461">
-        <v>17295</v>
+        <v>0</v>
       </c>
       <c r="J461" t="str">
-        <v/>
+        <v>An open-source project homepage website for desktop browsers where visitors can read what the project does, see recent updates, browse the main features, and find a link to the code repository, so anyone who stumbles across it immediately understands what the project is about and how to get started with it.</v>
       </c>
       <c r="K461" t="str">
-        <v/>
+        <v>一个开源项目首页网站，面向桌面浏览器，访问者可以了解项目做什么、看到最近的更新、浏览主要功能，还能找到代码库的链接，这样任何发现这个项目的人都能立即明白项目是什么，怎么开始用。</v>
       </c>
       <c r="L461" t="str">
-        <v>[q_web_068_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="462">
@@ -17956,19 +17956,19 @@
         <v>medium</v>
       </c>
       <c r="H462">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I462">
-        <v>22281</v>
+        <v>0</v>
       </c>
       <c r="J462" t="str">
-        <v/>
+        <v>Make a web app that works as a personal tech portfolio site where I can show off the projects I've built and the skills I've picked up, with a section for each project that includes a description and a link to try it out, all viewable nicely in a desktop browser so anyone who visits can get a real sense of what I do.</v>
       </c>
       <c r="K462" t="str">
-        <v/>
+        <v>做一个网页应用，作为个人技术作品集网站，可以展示我构建的项目和学到的技能，每个项目都有一个区域，包含描述和试用它的链接，在桌面浏览器里看起来都很不错，这样来访的人能真实感受到我做的东西。</v>
       </c>
       <c r="L462" t="str">
-        <v>[q_web_068_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="463">
@@ -17994,19 +17994,19 @@
         <v>medium</v>
       </c>
       <c r="H463">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="I463">
-        <v>19140</v>
+        <v>0</v>
       </c>
       <c r="J463" t="str">
-        <v/>
+        <v>Need a web app for building out my personal tech brand — something that works as a website where I can put my name and what I specialize in at the top, then list out projects I've worked on with some context about each one, and also link to where people can follow my writing or find my social profiles, so the whole thing feels like a home base for my work online when people look me up in a desktop browser.</v>
       </c>
       <c r="K463" t="str">
-        <v/>
+        <v>需要一个网页应用来打造个人技术品牌——一个网站，我可以在最上面写上自己的名字和专精领域，然后列出我做过的项目，附上每个项目的一些背景信息，还能链接到人们可以关注我的写作或找到我社交资料的地方，这样整个东西就成了我工作的根据地，桌面浏览器访问时感觉特别贴切。</v>
       </c>
       <c r="L463" t="str">
-        <v>[q_web_068_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="464">
@@ -18032,19 +18032,19 @@
         <v>medium</v>
       </c>
       <c r="H464">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I464">
-        <v>18349</v>
+        <v>0</v>
       </c>
       <c r="J464" t="str">
-        <v/>
+        <v>Need a web app that works as an interactive developer resume where you can browse my work experience and skills like a normal resume but also try out a little live coding area where visitors can type and run a small snippet right there in the browser, so it's actually fun to look at and shows what I can do instead of just reading a list of bullet points.</v>
       </c>
       <c r="K464" t="str">
-        <v/>
+        <v>需要一个网页应用，作为一份交互式开发者简历，可以像看普通简历一样浏览我的工作经历和技能，但还能在一个实时编码区域里尝试，访问者可以在浏览器里直接敲代码、运行小片段，这样看起来就很有意思，能真实展示我能做什么，而不只是读一堆项目符号。</v>
       </c>
       <c r="L464" t="str">
-        <v>[q_web_068_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="465">
@@ -18070,19 +18070,19 @@
         <v>medium</v>
       </c>
       <c r="H465">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I465">
-        <v>24096</v>
+        <v>0</v>
       </c>
       <c r="J465" t="str">
-        <v/>
+        <v>Make a website that showcases an engineering team — who's on it, what they each work on, and what the team as a whole is good at — with a section that gives a feel for the team culture and maybe some of the interesting problems they've solved together, so when people visit on a desktop browser they come away understanding what makes this particular team worth knowing about.</v>
       </c>
       <c r="K465" t="str">
-        <v/>
+        <v>做一个网站来展示一支工程团队——谁在团队里、各自做什么、整支团队的强项——还有一个区域能展现团队文化的氛围，也许还有一些他们一起解决过的有趣问题，这样当人们在桌面浏览器访问时，就能理解这支特别的团队为什么值得了解。</v>
       </c>
       <c r="L465" t="str">
-        <v>[q_web_068_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="466">
@@ -18108,19 +18108,19 @@
         <v>medium</v>
       </c>
       <c r="H466">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I466">
-        <v>22429</v>
+        <v>0</v>
       </c>
       <c r="J466" t="str">
-        <v/>
+        <v>Make a web app for a personal tech blog where I can write and publish posts about things I'm learning or building, organize them by topic so readers can browse by what interests them, and have each post look clean and readable on a desktop browser so it's pleasant to actually sit and read through.</v>
       </c>
       <c r="K466" t="str">
-        <v/>
+        <v>做一个网页应用，作为个人技术博客，可以写和发布我正在学的或构建的东西相关的文章，按主题组织它们，这样读者可以按兴趣浏览，每篇文章在桌面浏览器里看起来整洁易读，这样真的很舒服坐下来一篇篇读。</v>
       </c>
       <c r="L466" t="str">
-        <v>[q_web_069_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="467">
@@ -18146,19 +18146,19 @@
         <v>medium</v>
       </c>
       <c r="H467">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I467">
-        <v>26278</v>
+        <v>0</v>
       </c>
       <c r="J467" t="str">
-        <v/>
+        <v>Need a web app for writing and storing RFC and design documents, where I can create a new doc, write out the proposal with sections for background and the actual plan, and then have all the docs listed together so teammates can find and read them easily in a desktop browser, with each doc showing who wrote it and when.</v>
       </c>
       <c r="K467" t="str">
-        <v/>
+        <v>需要一个网页应用，用来写和存储 RFC 和设计文档，可以创建新文档，写出背景部分和实际计划的提案，然后把所有文档列在一起，这样团队成员可以在桌面浏览器上轻松找到和阅读，每份文档都显示作者和日期。</v>
       </c>
       <c r="L467" t="str">
-        <v>[q_web_069_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="468">
@@ -18184,19 +18184,19 @@
         <v>medium</v>
       </c>
       <c r="H468">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="I468">
-        <v>21302</v>
+        <v>0</v>
       </c>
       <c r="J468" t="str">
-        <v/>
+        <v>Build a web app for publishing a product changelog, where each update gets its own entry with a date, a version label, and a short description of what changed, all displayed in a clean timeline on the browser so users can scroll back and see the history of everything that's been released over time.</v>
       </c>
       <c r="K468" t="str">
-        <v/>
+        <v>做一个网页应用来发布产品变更日志，每次更新都有自己的条目，包含日期、版本标签和变动的简短说明，都显示在浏览器的一个清晰时间线上，这样用户可以向后滚动，看到所有历史发布的演进过程。</v>
       </c>
       <c r="L468" t="str">
-        <v>[q_web_069_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="469">
@@ -18222,19 +18222,19 @@
         <v>medium</v>
       </c>
       <c r="H469">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I469">
-        <v>20661</v>
+        <v>0</v>
       </c>
       <c r="J469" t="str">
-        <v/>
+        <v>Build a web app for a weekly tech newsletter where each issue gets its own entry with a date and a curated list of interesting articles and tools with short notes on each one, all browsable in a desktop browser so readers can flip back through past issues and find things they remember seeing before.</v>
       </c>
       <c r="K469" t="str">
-        <v/>
+        <v>做一个网页应用作为周技术新闻通讯，每期都有自己的条目，包含日期和精选的有趣文章和工具列表，附上每一项的简短说明，在桌面浏览器里都可以浏览，这样读者可以往回翻之前的期刊，找到他们记得看过的东西。</v>
       </c>
       <c r="L469" t="str">
-        <v>[q_web_069_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="470">
@@ -18260,19 +18260,19 @@
         <v>medium</v>
       </c>
       <c r="H470">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I470">
-        <v>19936</v>
+        <v>0</v>
       </c>
       <c r="J470" t="str">
-        <v/>
+        <v>Need a web app for an engineering team handbook and onboarding portal, where new folks joining the team can find all the basic stuff they need to know — how things are set up, who to talk to for what, common tools and how to use them — organized into a simple browsable structure on a desktop browser so everything is actually findable instead of buried in someone's notes.</v>
       </c>
       <c r="K470" t="str">
-        <v/>
+        <v>需要一个网页应用，作为工程团队的员工手册和入职门户，新员工加入团队时可以找到所有基础信息——系统怎么设置、有什么问题该找谁、常用工具和怎么用——按一个清晰的可浏览结构组织，在桌面浏览器上，这样所有东西真的能找到，而不是埋在某人的笔记里。</v>
       </c>
       <c r="L470" t="str">
-        <v>[q_web_069_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="471">
@@ -18298,19 +18298,19 @@
         <v>medium</v>
       </c>
       <c r="H471">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I471">
-        <v>21907</v>
+        <v>0</v>
       </c>
       <c r="J471" t="str">
-        <v/>
+        <v>Create a browser-based tool for a software team to browse and manage architecture decision records, where each record has a title, a short explanation of the problem, the decision made, and the reasoning behind it, and the home screen of the app shows all the records listed out so anyone on the team can quickly find past decisions without digging through old meeting notes.</v>
       </c>
       <c r="K471" t="str">
-        <v/>
+        <v>做一个浏览器工具，让软件团队浏览和管理架构决策记录，每条记录都有标题、问题的简短说明、做出的决策、以及背后的理由，应用的首页把所有记录列出来，这样团队任何人都能快速找到过去的决策，不用挖旧的会议记录。</v>
       </c>
       <c r="L471" t="str">
-        <v>[q_web_069_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="472">
@@ -18336,19 +18336,19 @@
         <v>medium</v>
       </c>
       <c r="H472">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I472">
-        <v>18497</v>
+        <v>0</v>
       </c>
       <c r="J472" t="str">
-        <v/>
+        <v>An open-source project landing website where visitors can get the gist of what the project does right away, see a quick demo or screenshot, find installation instructions, and click through to the repo, all laid out nicely for desktop browsers so it actually makes people want to try the thing out.</v>
       </c>
       <c r="K472" t="str">
-        <v/>
+        <v>一个开源项目登陆页网站，访问者能立即看到项目做什么，看到快速演示或截图，找到安装说明，点击链接到代码库，全部为桌面浏览器设计，看起来精心布局，这样真的能吸引人去试试这东西。</v>
       </c>
       <c r="L472" t="str">
-        <v>[q_web_070_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="473">
@@ -18374,19 +18374,19 @@
         <v>medium</v>
       </c>
       <c r="H473">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I473">
-        <v>17587</v>
+        <v>0</v>
       </c>
       <c r="J473" t="str">
-        <v/>
+        <v>Build a web app for a hackathon event site where participants can read about the theme and rules, see the schedule of sessions and deadlines, and browse the list of submitted projects with short descriptions, all in a desktop browser so organizers and teams can keep up with everything happening during the event.</v>
       </c>
       <c r="K473" t="str">
-        <v/>
+        <v>做一个网页应用作为黑客马拉松活动网站，参与者可以读到主题和规则，看到会议和截止时间的日程，浏览提交项目的列表和简短说明，都在桌面浏览器里，这样组织者和团队可以跟上活动期间发生的所有事。</v>
       </c>
       <c r="L473" t="str">
-        <v>[q_web_070_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="474">
@@ -18412,19 +18412,19 @@
         <v>medium</v>
       </c>
       <c r="H474">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="I474">
-        <v>19777</v>
+        <v>0</v>
       </c>
       <c r="J474" t="str">
-        <v/>
+        <v>Build a web app for a developer conference website where visitors can read about the event, browse the speaker lineup with bios and talk topics, and see the full schedule laid out by time slot, all viewable on a desktop browser so attendees can plan out which sessions they want to catch.</v>
       </c>
       <c r="K474" t="str">
-        <v/>
+        <v>做一个网页应用作为开发者大会网站，访问者可以读到活动信息，浏览演讲者名单带着个人简介和讲题，看到按时间段布局的完整日程，都在桌面浏览器上可见，这样参会者可以计划好想参加哪些会议。</v>
       </c>
       <c r="L474" t="str">
-        <v>[q_web_070_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="475">
@@ -18450,19 +18450,19 @@
         <v>medium</v>
       </c>
       <c r="H475">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I475">
-        <v>20530</v>
+        <v>0</v>
       </c>
       <c r="J475" t="str">
-        <v/>
+        <v>An API-first SaaS launch site for desktop browsers where the whole thing is built around showing developers exactly what they can do with the API right from the top — a big friendly explanation of what the product does, a clear area showing sample requests and what comes back, and a part where people can sign up or grab an API key to try it out, all in one smooth web app that flows from "what is this" to "let me try it" without any friction.</v>
       </c>
       <c r="K475" t="str">
-        <v/>
+        <v>一个面向 API 优先的 SaaS 发布网站，面向桌面浏览器，整个网站都围绕向开发者展示他们用 API 能做什么——从最上面开始有一个大的、友好的产品说明，明确区域展示示例请求和返回值，还有地方让人注册或获取 API 密钥来试用，全部在一个平顺的网页应用里，从『这是什么』流畅过渡到『让我试试』，没有任何摩擦。</v>
       </c>
       <c r="L475" t="str">
-        <v>[q_web_070_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="476">
@@ -18488,19 +18488,19 @@
         <v>medium</v>
       </c>
       <c r="H476">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I476">
-        <v>19836</v>
+        <v>0</v>
       </c>
       <c r="J476" t="str">
-        <v/>
+        <v>Create a web app for showing off a developer SDK where people can actually play with it right in the browser — the main thing is a split layout where one side has the code you can type into and tweak, and the other side shows you what that code does when it runs, plus a section listing out all the different things the SDK can do with little example snippets for each one so people can jump in and start tinkering right away on desktop.</v>
       </c>
       <c r="K476" t="str">
-        <v/>
+        <v>做一个网页应用来展示开发者 SDK，人们真的可以在浏览器里试用——主要是一个分栏布局，左边是你可以输入和调整的代码，右边展示代码运行的效果，加上一个区域列出 SDK 能做的所有不同东西，每个都带有小例子片段，这样人们可以立即跳进来开始在桌面摆弄。</v>
       </c>
       <c r="L476" t="str">
-        <v>[q_web_070_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="477">
@@ -18526,19 +18526,19 @@
         <v>medium</v>
       </c>
       <c r="H477">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I477">
-        <v>18462</v>
+        <v>0</v>
       </c>
       <c r="J477" t="str">
-        <v/>
+        <v>Make a web app for an open-source project that gives a proper shoutout to everyone who chips in money to keep it going — sponsors get their logos and names up in a nice highlighted spot, and individual backers get listed out too, maybe grouped by how much they give, so when someone lands on the site they can immediately see the community of people behind the project and feel like joining in is worth it.</v>
       </c>
       <c r="K477" t="str">
-        <v/>
+        <v>做一个网页应用为开源项目给予适当的感谢，对所有贡献资金的人——赞助者的标志和名字出现在一个漂亮突出的地方，单个支持者也会被列出来，也许按捐款金额分组，这样当有人登陆网站时，他们能立即看到项目背后的社区，感受到加入的价值。</v>
       </c>
       <c r="L477" t="str">
-        <v>[q_web_070_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="478">
@@ -18564,19 +18564,19 @@
         <v>medium</v>
       </c>
       <c r="H478">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I478">
-        <v>22359</v>
+        <v>0</v>
       </c>
       <c r="J478" t="str">
-        <v/>
+        <v>A donation and sponsor tracker for an open-source tool, basically a web app where someone can put in their project info and it shows a clean page with how much has been raised, who the supporters are, and a spot where new people can click to contribute — the whole hassle I want to remove is manually updating a readme or spreadsheet every time someone new pitches in, so this just keeps it all in one place that updates itself for desktop browsers.</v>
       </c>
       <c r="K478" t="str">
-        <v/>
+        <v>一个开源工具的捐款和赞助追踪器，基本上是一个网页应用，有人可以输入项目信息，它展示一个整洁的页面显示募资金额、支持者都是谁、还有新人可以点击贡献的地方——我要去掉的麻烦是每次有人贡献时都要手动更新 readme 或电子表格，这个把所有东西都放在一个自动更新的地方，在桌面浏览器上运行。</v>
       </c>
       <c r="L478" t="str">
-        <v>[q_web_071_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="479">
@@ -18602,19 +18602,19 @@
         <v>medium</v>
       </c>
       <c r="H479">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="I479">
-        <v>18881</v>
+        <v>0</v>
       </c>
       <c r="J479" t="str">
-        <v/>
+        <v>Make a web app that handles Pro plan subscriptions for a developer tool, where users can see what they get with the free tier versus the paid one, pick their billing period, and actually upgrade without having to email anyone or fill out a form — the whole point is so people can self-serve the upgrade on desktop without me having to manually handle it every time someone wants to pay.</v>
       </c>
       <c r="K479" t="str">
-        <v/>
+        <v>做一个网页应用来处理开发者工具的专业版订阅，用户可以看到免费版和付费版的差别，选择计费周期，然后真的可以升级，不用发邮件或填表格——关键是要让人们在桌面上自助升级，这样我就不用每次有人想付钱时都手动处理。</v>
       </c>
       <c r="L479" t="str">
-        <v>[q_web_071_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="480">
@@ -18640,19 +18640,19 @@
         <v>medium</v>
       </c>
       <c r="H480">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I480">
-        <v>21004</v>
+        <v>0</v>
       </c>
       <c r="J480" t="str">
-        <v/>
+        <v>Build a web app that works like a marketplace where people can browse different APIs, see what each one costs per request or per month, and manage how much they're actually spending without any surprise bills at the end of the month — the app should have a usage tracking area where you can see your current spend and set yourself a limit, and a listing of available APIs with their pricing so choosing one is straightforward on desktop browsers.</v>
       </c>
       <c r="K480" t="str">
-        <v/>
+        <v>做一个网页应用就像一个市集，人们可以浏览不同的 API，看每个 API 的价格——按请求或按月——然后管理他们实际的花费，不用担心月底会有惊喜账单——应用应该有一个使用跟踪区域，你可以看到当前花费并设置一个限额，还有可用 API 的列表和定价信息，这样选择就很直白，在桌面浏览器上。</v>
       </c>
       <c r="L480" t="str">
-        <v>[q_web_071_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="481">
@@ -18678,19 +18678,19 @@
         <v>medium</v>
       </c>
       <c r="H481">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I481">
-        <v>19837</v>
+        <v>0</v>
       </c>
       <c r="J481" t="str">
-        <v/>
+        <v>Build a web app for selling and managing enterprise licenses for an open-source project, where companies can fill out what they need, see the license options, and complete a purchase without having to go back and forth over email — also a place where existing license holders can log in and check their license status or download their agreement, all running in desktop browsers so the whole process is self-serve.</v>
       </c>
       <c r="K481" t="str">
-        <v/>
+        <v>做一个网页应用来销售和管理开源项目的企业许可证，公司可以填写他们的需求，看到许可证选项，完成购买，不用反复发邮件——还有一个地方让现有许可证持有者登录、查看许可状态或下载协议，全部在桌面浏览器运行，所以整个流程是自助的。</v>
       </c>
       <c r="L481" t="str">
-        <v>[q_web_071_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="482">
@@ -18716,19 +18716,19 @@
         <v>medium</v>
       </c>
       <c r="H482">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="I482">
-        <v>20221</v>
+        <v>0</v>
       </c>
       <c r="J482" t="str">
-        <v/>
+        <v>Create a web app that lays out all the pricing plans for a developer tool side by side so you can actually figure out what you're getting for the money — each plan should show the features it includes, the monthly and yearly price, and a button to get started, and there should be a simple way to toggle between the billing periods so comparing is easy without having to open a spreadsheet to do the math, all for desktop browsers.</v>
       </c>
       <c r="K482" t="str">
-        <v/>
+        <v>做一个网页应用，把开发者工具的所有定价方案并排展示，这样你真的能搞清楚自己花多少钱；每个方案都应该显示包含的功能、按月和按年的价格，还有『开始』按钮，应该有简单方式在计费周期间切换，这样对比就很容易，不用拿出电子表格算数，全部为桌面浏览器。</v>
       </c>
       <c r="L482" t="str">
-        <v>[q_web_071_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="483">
@@ -18754,19 +18754,19 @@
         <v>medium</v>
       </c>
       <c r="H483">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="I483">
-        <v>19913</v>
+        <v>0</v>
       </c>
       <c r="J483" t="str">
-        <v/>
+        <v>A client-facing project tracker for a tech consulting firm, basically a web app where each client logs in and sees only their own projects — what's in progress, what's done, any files shared with them, and a way to send a quick message to the team without having to email back and forth — the idea is clients stop asking "what's the status" because they can just check it themselves on desktop browsers.</v>
       </c>
       <c r="K483" t="str">
-        <v/>
+        <v>一个面向客户的项目追踪器，为技术顾问公司服务，基本上是一个网页应用，每个客户登录后只能看到自己的项目——什么在进行、什么完成了、任何与他们分享的文件、还有快速给团队发消息的方式，不用在邮件来回往复——想法是客户不用再问『进展怎样』，因为他们可以在桌面浏览器上自己查。</v>
       </c>
       <c r="L483" t="str">
-        <v>[q_web_071_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="484">
@@ -18792,19 +18792,19 @@
         <v>medium</v>
       </c>
       <c r="H484">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I484">
-        <v>20035</v>
+        <v>0</v>
       </c>
       <c r="J484" t="str">
-        <v/>
+        <v>Make a technical docs and wiki app for desktop browsers where you can write and organize articles by topic, have a left-side list of all the pages so you can jump around quickly, and search through everything to find what you need — I want each article to support things like code blocks and headings, and a way to link between pages so related topics connect to each other naturally.</v>
       </c>
       <c r="K484" t="str">
-        <v/>
+        <v>做一个技术文档和 wiki 应用面向桌面浏览器，可以写和按主题组织文章，左边有所有页面的列表，可以快速跳转，还能在所有内容里搜索找你需要的——我想每篇文章都支持代码块和标题这样的东西，还能在页面间链接，这样相关话题会自然地连在一起。</v>
       </c>
       <c r="L484" t="str">
-        <v>[q_web_072_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="485">
@@ -18830,19 +18830,19 @@
         <v>medium</v>
       </c>
       <c r="H485">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="I485">
-        <v>19915</v>
+        <v>0</v>
       </c>
       <c r="J485" t="str">
-        <v/>
+        <v>Create a web app for browsing API reference docs where every endpoint is listed out clearly on the left side so you can click through to each one, and when you pick one it shows you exactly what it takes as input, what it sends back, and a sample request and response — it should be easy to copy the examples and the whole thing should be easy to navigate on desktop with a keyboard so looking things up is fast.</v>
       </c>
       <c r="K485" t="str">
-        <v/>
+        <v>做一个网页应用来浏览 API 参考文档，每个端点都清晰列在左边，可以点击进入每一个，选中时会显示它的输入、输出、样例请求和响应——应该容易复制例子，在桌面上用键盘导航应该很顺手，所以查询东西很快。</v>
       </c>
       <c r="L485" t="str">
-        <v>[q_web_072_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="486">
@@ -18868,19 +18868,19 @@
         <v>medium</v>
       </c>
       <c r="H486">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="I486">
-        <v>18661</v>
+        <v>0</v>
       </c>
       <c r="J486" t="str">
-        <v/>
+        <v>Build a tutorial site web app for desktop browsers where tutorials are organized by topic and difficulty level, each one has a clear step-by-step layout with numbered steps and code examples, and there's a way to mark which ones you've finished so you know where you left off — I also want a search box at the top so if I know what I'm looking for I can get there without scrolling through everything.</v>
       </c>
       <c r="K486" t="str">
-        <v/>
+        <v>做一个教程网站网页应用面向桌面浏览器，教程按主题和难度级别组织，每个都有清晰的分步布局，编号步骤和代码例子，有办法标记你已完成的教程，这样你知道上次停在哪里——我还想要顶部有个搜索框，这样如果我知道自己在找什么，可以直接过去，不用滚遍所有东西。</v>
       </c>
       <c r="L486" t="str">
-        <v>[q_web_072_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="487">
@@ -18906,19 +18906,19 @@
         <v>medium</v>
       </c>
       <c r="H487">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="I487">
-        <v>22107</v>
+        <v>0</v>
       </c>
       <c r="J487" t="str">
-        <v/>
+        <v>Make a web app that works as an interactive learning tool where each lesson has a mix of reading and hands-on exercises you complete right on the page — things like fill-in-the-blank, multiple choice, or little tasks that check your answer and tell you if you're right — the lessons should be organized in order so you know what to do next, and your progress should be saved so you can come back to it on desktop browsers.</v>
       </c>
       <c r="K487" t="str">
-        <v/>
+        <v>做一个网页应用作为交互式学习工具，每堂课都混合了阅读和实践练习，直接在页面上完成——比如填空、选择题、或检查答案并告诉你对不对的小任务——课程应该按顺序组织，这样你知道下一步做什么，进度应该被保存，这样你可以在桌面浏览器上回来继续。</v>
       </c>
       <c r="L487" t="str">
-        <v>[q_web_072_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="488">
@@ -18944,19 +18944,19 @@
         <v>medium</v>
       </c>
       <c r="H488">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="I488">
-        <v>21031</v>
+        <v>0</v>
       </c>
       <c r="J488" t="str">
-        <v/>
+        <v>Need a browser-based coding challenge tool where challenges are organized from beginner to harder so you always know what to try next — each challenge shows the problem, gives you a place to write your solution right in the browser, and checks whether your answer works and gives you feedback, and there's a list showing which ones you've already completed so you can track how far you've gotten.</v>
       </c>
       <c r="K488" t="str">
-        <v/>
+        <v>需要一个浏览器编程挑战工具，挑战按从初级到更难的程度组织，这样你总是知道接下来要试什么——每个挑战展示问题，给你一个地方在浏览器里写解决方案，检查答案是否有效并给反馈，还有个列表显示你已完成的挑战，这样你能跟踪自己走了多远。</v>
       </c>
       <c r="L488" t="str">
-        <v>[q_web_072_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="489">
@@ -18982,19 +18982,19 @@
         <v>medium</v>
       </c>
       <c r="H489">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="I489">
-        <v>23051</v>
+        <v>0</v>
       </c>
       <c r="J489" t="str">
-        <v/>
+        <v>Make a web app for studying system design interview topics where each topic has a written explanation and a diagram you can click on to see notes about specific parts — the topics should be listed out on one side so you can move between them easily, and there should be a way to mark ones you want to review again, all viewable on desktop browsers so you can sit down and study properly.</v>
       </c>
       <c r="K489" t="str">
-        <v/>
+        <v>做一个网页应用来学习系统设计面试主题，每个主题都有书面说明和一个图表，可以点击查看特定部分的笔记——主题应该列在一边，可以轻松在它们间移动，还应该有办法标记你想再审查的，全部在桌面浏览器上可见，这样你可以坐下来好好学习。</v>
       </c>
       <c r="L489" t="str">
-        <v>[q_web_072_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="490">
@@ -19020,19 +19020,19 @@
         <v>medium</v>
       </c>
       <c r="H490">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I490">
-        <v>21397</v>
+        <v>0</v>
       </c>
       <c r="J490" t="str">
-        <v/>
+        <v>A forum web app for desktop browsers where people can post questions or start discussions grouped by topic, reply to each other in threaded conversations, and vote on posts so the good ones float up — I want a clean list of all the categories on the home screen so it's easy to find where to go, and each thread should show who posted and when so you can tell what's current.</v>
       </c>
       <c r="K490" t="str">
-        <v/>
+        <v>一个论坛网页应用面向桌面浏览器，人们可以发布问题或按主题分组的讨论，在线程式对话里互相回复，通过投票让好的帖子浮上来——我想首页有一个所有类别的清晰列表，这样容易找到去哪里，每条线程应该显示谁发布的、什么时候，这样你能看出什么是现在的。</v>
       </c>
       <c r="L490" t="str">
-        <v>[q_web_073_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="491">
@@ -19058,19 +19058,19 @@
         <v>medium</v>
       </c>
       <c r="H491">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="I491">
-        <v>18464</v>
+        <v>0</v>
       </c>
       <c r="J491" t="str">
-        <v/>
+        <v>Create a Q&amp;A web app for desktop browsers where people can post questions, others can write answers, and the community can vote on which answers are most helpful so the best one rises to the top — there should be a way to browse questions by topic or search for something specific, and each question should clearly show how many answers it has so you know if it's already been solved before clicking in.</v>
       </c>
       <c r="K491" t="str">
-        <v/>
+        <v>做一个问答网页应用面向桌面浏览器，人们可以发布问题，别人可以写答案，社区可以投票哪些答案最有帮助，最好的答案就会浮上来——应该有办法按主题浏览问题或搜索特定的东西，每个问题应该清楚显示它有多少个答案，这样你知道点击前它是否已经被解答。</v>
       </c>
       <c r="L491" t="str">
-        <v>[q_web_073_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="492">
@@ -19096,19 +19096,19 @@
         <v>medium</v>
       </c>
       <c r="H492">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I492">
-        <v>21640</v>
+        <v>0</v>
       </c>
       <c r="J492" t="str">
-        <v/>
+        <v>A Discord community landing page web app for desktop browsers where the whole point is to invite people to join a server — it shows what the community is about, maybe some highlights of what gets discussed there, a count of how many members are in it, and a big obvious button to join, so anyone who lands on it immediately understands what the community is for and feels like jumping in.</v>
       </c>
       <c r="K492" t="str">
-        <v/>
+        <v>一个 Discord 社区登陆页网页应用面向桌面浏览器，关键点就是邀请人们加入服务器——显示社区是关于什么的，也许一些那里讨论内容的亮点，有多少成员的数字，还有个明显的『加入』按钮，这样登陆的人立即明白社区是干什么的，有加入的冲动。</v>
       </c>
       <c r="L492" t="str">
-        <v>[q_web_073_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="493">
@@ -19134,19 +19134,19 @@
         <v>medium</v>
       </c>
       <c r="H493">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I493">
-        <v>20431</v>
+        <v>0</v>
       </c>
       <c r="J493" t="str">
-        <v/>
+        <v>Make a web app for an open-source community where people can see all the projects under the umbrella in one place, check out who's contributing, and find out how to get involved — the home area should show featured projects with a quick description, and there should be a simple way to browse all of them or filter by what kind of project it is, all working in a browser on desktop.</v>
       </c>
       <c r="K493" t="str">
-        <v/>
+        <v>做一个网页应用作为开源社区，人们可以在一个地方看到这个伞形组织下的所有项目，查看谁在贡献，找出怎么参与——首页区域应该展示精选项目带着快速说明，应该有简单方式浏览全部或按项目类型筛选，全部在桌面浏览器上工作。</v>
       </c>
       <c r="L493" t="str">
-        <v>[q_web_073_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="494">
@@ -19172,19 +19172,19 @@
         <v>medium</v>
       </c>
       <c r="H494">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="I494">
-        <v>18443</v>
+        <v>0</v>
       </c>
       <c r="J494" t="str">
-        <v/>
+        <v>Need a web app for developers to share little bits of code they find useful, where you can post a snippet with a title and description, and other people can browse through them, upvote the ones they like, and copy the code straight from the page — the app should let you filter by programming language so finding something in a specific language is quick, and it all runs in the browser on desktop without needing to sign up just to browse.</v>
       </c>
       <c r="K494" t="str">
-        <v/>
+        <v>需要一个网页应用让开发者分享他们发现的有用的代码片段，可以发布一个片段带着标题和说明，别人可以浏览它们，给他们喜欢的投上一票，直接从页面复制代码——应用应该让你按编程语言筛选，这样用特定语言找东西很快，全部在桌面浏览器里运行，不用注册就能浏览。</v>
       </c>
       <c r="L494" t="str">
-        <v>[q_web_073_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="495">
@@ -19210,19 +19210,19 @@
         <v>medium</v>
       </c>
       <c r="H495">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I495">
-        <v>21697</v>
+        <v>0</v>
       </c>
       <c r="J495" t="str">
-        <v/>
+        <v>Need a web app for browsing and discovering open-source projects where each project has a card with its name, what it does in plain language, and how active it is — you can filter by category or what language it's written in, and clicking a project takes you to a page with more details and a link to the actual repo, so finding something cool to use or contribute to is easy from desktop browsers.</v>
       </c>
       <c r="K495" t="str">
-        <v/>
+        <v>需要一个网页应用来浏览和发现开源项目，每个项目都有一个卡片显示名字、用简明语言说明它做什么、还有它有多活跃——可以按类别或它用什么编程语言筛选，点击项目会进到一个页面显示更多细节和实际代码库的链接，这样从桌面浏览器找到酷东西用或贡献就很容易。</v>
       </c>
       <c r="L495" t="str">
-        <v>[q_web_073_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="496">
@@ -19248,19 +19248,19 @@
         <v>medium</v>
       </c>
       <c r="H496">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I496">
-        <v>19272</v>
+        <v>0</v>
       </c>
       <c r="J496" t="str">
-        <v/>
+        <v>Build a web app that works as a playground for weird little interactive experiments — things you can poke at in the browser just to see what happens, like visual toys or small demos that respond to what you do with the mouse or keyboard, with a simple home screen listing all the experiments so you can jump between them, designed for desktop browsers where you have a proper screen and mouse to mess around with.</v>
       </c>
       <c r="K496" t="str">
-        <v/>
+        <v>做一个网页应用作为古怪的小交互实验的游乐场——你可以在浏览器里摆弄的东西，只是看看会怎样，比如视觉玩具或小演示，会对你的鼠标或键盘输入做出反应，首页有一个列表列出所有实验，你可以在它们间跳转，为桌面浏览器设计，这样你有真正的屏幕和鼠标来摆弄。</v>
       </c>
       <c r="L496" t="str">
-        <v>[q_web_074_001] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="497">
@@ -19286,19 +19286,19 @@
         <v>medium</v>
       </c>
       <c r="H497">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="I497">
-        <v>20380</v>
+        <v>0</v>
       </c>
       <c r="J497" t="str">
-        <v/>
+        <v>A handy little calculator toolkit web app for desktop browsers where you can pick from a bunch of different useful calculators in one place — things like unit conversion, percentage math, time zone differences, whatever comes in handy day to day — the home screen lists them all so you can find the one you want quickly, and each calculator is simple to use with clear inputs and the result shown right there.</v>
       </c>
       <c r="K497" t="str">
-        <v/>
+        <v>一个方便的小计算工具包网页应用面向桌面浏览器，你可以在一个地方从一堆不同的有用计算器里选——比如单位转换、百分比数学、时区差异、日常有用的各种东西——首页列出全部，这样可以快速找到你要的，每个计算器都简单易用，输入清晰，结果就显示在那儿。</v>
       </c>
       <c r="L497" t="str">
-        <v>[q_web_074_002] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="498">
@@ -19324,19 +19324,19 @@
         <v>medium</v>
       </c>
       <c r="H498">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="I498">
-        <v>21355</v>
+        <v>0</v>
       </c>
       <c r="J498" t="str">
-        <v/>
+        <v>Create a web app that pulls together useful developer resources all in one spot — libraries, tools, blogs, free APIs, whatever people actually use — organized by category so it's easy to browse, with a search box at the top for when you know what you're looking for, and each resource has a short description and a link so you know what it is before clicking through, all on desktop browsers.</v>
       </c>
       <c r="K498" t="str">
-        <v/>
+        <v>做一个网页应用，把有用的开发者资源都集合在一个地方——库、工具、博客、免费 API、人们真的在用的东西——按类别组织，这样容易浏览，顶部有搜索框用来你知道自己在找什么的时候，每个资源都有简短说明和链接，这样你知道点击前是什么，全部在桌面浏览器上。</v>
       </c>
       <c r="L498" t="str">
-        <v>[q_web_074_003] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="499">
@@ -19362,19 +19362,19 @@
         <v>medium</v>
       </c>
       <c r="H499">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I499">
-        <v>22023</v>
+        <v>0</v>
       </c>
       <c r="J499" t="str">
-        <v/>
+        <v>Build a developer tools directory web app for desktop browsers where people can browse a categorized list of tools — libraries, services, utilities — each with a short description, a link, and maybe a star rating or upvote count so you can tell what's popular, and there's a search bar and category filters at the top so finding the right kind of tool for what you're working on is quick and easy.</v>
       </c>
       <c r="K499" t="str">
-        <v/>
+        <v>做一个开发者工具目录网页应用面向桌面浏览器，人们可以浏览一个分类的工具列表——库、服务、实用程序——每个都带着简短说明、链接、也许还有星级或投票数，这样你可以看出什么受欢迎，顶部有搜索框和类别筛选，这样找到正确的工具来完成你正在做的事很快很容易。</v>
       </c>
       <c r="L499" t="str">
-        <v>[q_web_074_004] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="500">
@@ -19400,19 +19400,19 @@
         <v>medium</v>
       </c>
       <c r="H500">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="I500">
-        <v>24744</v>
+        <v>0</v>
       </c>
       <c r="J500" t="str">
-        <v/>
+        <v>Make a web app where I can test out different API endpoints and also set up fake server responses so I can tinker with how things behave without needing a real backend running — I want a left side where I type in the URL and pick the request type, and a right side that shows me what came back, and somewhere to define my own pretend responses that the tool will return when I hit a certain address.</v>
       </c>
       <c r="K500" t="str">
-        <v/>
+        <v>做一个网络应用，能让我测试不同的API端点，还能设置假的服务器响应，这样我就能在没有真实后端的情况下调试各种行为——左边放一个地方输入URL和选择请求类型，右边显示返回的结果，然后还要有个地方能定义我自己的虚拟响应，工具调用某个地址时就返回这些响应。</v>
       </c>
       <c r="L500" t="str">
-        <v>[q_web_074_005] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
     <row r="501">
@@ -19438,19 +19438,19 @@
         <v>medium</v>
       </c>
       <c r="H501">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I501">
-        <v>19685</v>
+        <v>0</v>
       </c>
       <c r="J501" t="str">
-        <v/>
+        <v>A regex playground tool for desktop browsers where I type a pattern on one side and paste in some sample text on the other side, and it highlights all the matching parts in real time as I adjust the pattern — I want it to also show me a little breakdown of what each chunk of the pattern actually means in plain words, so I can learn as I go without having to look stuff up separately.</v>
       </c>
       <c r="K501" t="str">
-        <v/>
+        <v>一个正则表达式练习工具，在桌面浏览器上用，左边输入正则规则，右边粘贴示例文本，当我修改规则时实时高亮显示匹配的部分——还要给我看一下规则中各个部分的含义解释，用通俗的话说明，这样我可以边用边学，不用另外查资料。</v>
       </c>
       <c r="L501" t="str">
-        <v>[q_web_074_006] claude 退出码=1</v>
+        <v/>
       </c>
     </row>
   </sheetData>
